--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B13D122-A5DE-40B9-946A-7313FF276DC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665C514-1209-43BD-9324-6F755CB18A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="171">
   <si>
     <t>id</t>
   </si>
@@ -83,12 +83,6 @@
   </si>
   <si>
     <t>臺北市中山區新庄里吉林路456巷10號</t>
-  </si>
-  <si>
-    <t xml:space="preserve">平時｜預訂制（麻糬、冷泡茶以預先訂購為主）
-臺北數位藝術節期間｜限定開放營業
-實際開放日期與時間依官方 Facebook 公告 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>02-25957137</t>
@@ -171,23 +165,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Gallery188</t>
-  </si>
-  <si>
-    <t>臺北市大同區至聖里承德路三段188號</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>周一  11:00-19:00
-周二  11:00-19:00
-周三  公休
-周四  公休
-周五  公休
-周六  13:00-18:00
-周日  13:00-18:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>0966120302</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -202,11 +179,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>IG：https://www.instagram.com/gallery188_/
-FB：https://www.facebook.com/p/Gallery-188%E6%9D%89%E7%95%9D%E8%97%9D%E8%A1%93-61575686574065/</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>address</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -223,22 +195,12 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>No. 188, Sec. 3, Chengde Rd., Datong Dist., Taipei City 103034, Taiwan (R.O.C.)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>Opening Hours</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>English Introduction</t>
     <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Regular Hours | By reservation only
-Mochi and cold-brew tea are primarily available by pre-order.
-During the Taipei Digital Art Festival | Open on selected dates
-Please refer to the official Facebook page for the latest opening dates and hours.</t>
   </si>
   <si>
     <t>Mon–Wed 19:30–01:00
@@ -249,11 +211,6 @@
   <si>
     <t>Mon–Thu 12:00–19:00
 Fri–Sun 12:00–15:00</t>
-  </si>
-  <si>
-    <t>Mon–Tue 11:00–19:00
-Wed–Fri Closed
-Sat–Sun 13:00–18:00</t>
   </si>
   <si>
     <t>Tucked away in an alley off Jilin Road, emhanuel is a multidisciplinary space that brings together handmade food, coffee, design, and everyday aesthetics. At its heart are handmade mochi, with flavors such as Joseph Peanut, Ruth Black Sesame, Jonah Red Bean, and Peter Pickled Mustard Greens, each carrying its own story and blessing. The shop also serves caffeine-free cold-brew buckwheat tea and hand-brewed coffee made with beans roasted in-house, offering visitors the warmth of handcrafted food and drink.
@@ -519,17 +476,6 @@
   <si>
     <t xml:space="preserve">官網：https://linktr.ee/isekaicafe_ungetsu
 </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Isekaicafe Ungetsu is a cosplay-themed café tucked away in an alley off Shuangcheng Street. Built around the fantasy setting of an “adventurers’ guild in a dark castle,” it offers an experience distinct from traditional maid cafés, inviting every guest to step into the role of an adventurer embarking on a fantastical journey.
-The guild staff are cosplayers portraying characters of different races and personalities. With a stage and sound system, the café also hosts occasional performances and fan gatherings. Its imaginative dishes, including the fantasy-inspired “Bone-in Monster Meat,” have become favorites among visitors.
-Combining themed cuisine with interactive experiences, Isekaicafe Ungetsu brings the world of fantasy adventure to life.</t>
-  </si>
-  <si>
-    <t>異世界咖啡館•澐月是位於雙城街巷弄內的 Cosplay 主題咖啡館，設定「黑暗城堡風的冒險者公會」世界觀，與傳統女僕咖啡廳做區隔，讓顧客化身「冒險者」展開奇幻旅程。
-店內的公會職員皆由不同種族與性格的 Coser 擔任，備有舞台及音響，不定期舉辦表演和同好聚會，彷彿從漫畫中走出來的「魔獸帶骨肉佐黃金降」在圈內更是廣受好評。
-特色餐點與豐富互動機制，絕對能滿足顧客對冒險生活的嚮往。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -856,16 +802,92 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>10:00-20:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>三樓家以馬內利食研室</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>FB：https://www.facebook.com/love3F/?locale=zh_TW
 IG：https://www.instagram.com/3flove_home/?hl=am-et</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>臺北數位藝術節期間｜周末限定 OPEN HOUSE
+11/01（日）14:00-17:00
+11/07（六）、11/08（日）、11/14（六）、11/15（日）10:30-16:30
+白晝之夜限定 | 活動響應延長開放
+10/31（六）12:00-20:00，預留限定麻糬現場購買
+平時｜預訂制（麻糬、冷泡茶以預先訂購為主）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>During the Taipei Digital Art Festival | Weekend OPEN HOUSE
+Nov. 1 (Sun) 14:00–17:00
+Nov. 7 (Sat), Nov. 8 (Sun), Nov. 14 (Sat) &amp; Nov. 15 (Sun) 10:30–16:30
+Nuit Blanche Taipei | Extended Opening Hours
+Oct. 31 (Sat) 12:00–20:00
+A limited quantity of mochi will be available for on-site purchase.
+Regular Hours | By Reservation Only
+Mochi and cold-brew tea are primarily available by pre-order.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>12:00-20:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>官網：https://www.samsart.net/
+IG：https://www.instagram.com/gallery188_/
+FB：https://www.facebook.com/p/Gallery-188%E6%9D%89%E7%95%9D%E8%97%9D%E8%A1%93-61575686574065/</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallery 188（杉畝藝術有限公司、OhMyDeer Floral） </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallery 188（Sam’s Art Co. 、OhMyDeer Floral） </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>周六  13:00-18:00
+周日  13:00-18:00
+平日 | 預約參觀
+活動主題響應展覽 | 《在記憶折返以前》
+展期 10/10-11/8、10/17（六）15:00 開幕</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gallery 188座落於台北市大同區承德路三段188號，從捷運圓山站1號出口步行即可抵達。以當代藝術為核心，持續邀請新銳藝術家、設計師及跨領域創作者展出，也透過策展、品牌合作、講座與工作坊，讓作品走進城市日常。
+空間保留親近而安靜的觀看尺度，觀眾可以放慢腳步，細看影像、繪畫與裝置中的情感線索。邀請大家將這裡納入城市漫遊路線，在熱鬧活動之間，留一段時間給藝術與自己。
+《在記憶折返以前》，由台北雙人創作團體Fina與Tony共同展出。Fina以散文式數位影像收集街道、人物與生活片刻；Tony透過翻轉、鏡像與重組，將城市燈火化為影像詩。兩人的作品游移於具象與抽象之間，沿著光線、記憶與時間交會，邀請觀眾辨認那些尚未說完、仍在心中折返的感受。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gallery 188 is located at No. 188, Sec. 3, Chengde Rd., Datong District, Taipei, within walking distance of Exit 1 of Yuanshan MRT Station. With a focus on contemporary art, the gallery regularly presents works by emerging artists, designers, and interdisciplinary creators. Through curated exhibitions, brand collaborations, talks, and workshops, Gallery 188 brings art into the fabric of everyday urban life.
+The space offers an intimate and quiet setting for viewing, inviting visitors to slow down and discover the emotional threads woven through moving images, paintings, and installations. Gallery 188 welcomes visitors to make the space part of their journey through the city—to set aside a moment amid the bustle and spend some time with art and themselves.
+Before Memory Turns Back is a joint exhibition by Taipei-based artist duo Fina and Tony. Fina gathers fragments of streets, people, and everyday life through essayistic digital imagery, while Tony transforms the lights of the city into visual poetry through inversion, mirroring, and recomposition. Moving between the figurative and the abstract, their works trace intersections of light, memory, and time, inviting viewers to recognize feelings that remain unfinished and continue to return within.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Opening Hours
+Sat–Sun 13:00–18:00
+Weekdays | By Appointment
+Featured Exhibition | Before Memory Turns Back
+Exhibition Period | Oct. 10–Nov. 8
+Opening Reception | Oct. 17 (Sat), 15:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>「異世界咖啡館・澐月」是一間隱身於雙城街巷弄，以劍與魔法世界為背景、黑暗城堡風「冒險者公會」為舞台打造的沉浸式主題咖啡廳。
+來訪的顧客將化身踏入異世界的「冒險者」，由不同種族與性格的公會職員接待，透過場景佈置、角色設定、特色餐飲、任務與互動，共同展開一段奇幻旅程。
+店內亦設有舞台與音響，不定期舉辦表演、同好聚會與主題活動；從象徵討伐強敵的「炙燒歐克將軍蓋飯」到以傳說魔物為靈感打造的牛舌料理「米陶洛斯之吻」及各式異世界料理，希望讓每一次來訪不只是用餐，更像是在旅途中短暫踏入另一個世界，留下屬於自己的冒險故事。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Isekaicafe Ungetsu is an immersive themed café tucked away in the alleys of Shuangcheng Street. Set in a world of swords and magic, the café takes the form of an “Adventurers’ Guild” housed within a dark castle.
+Visitors step into this otherworld as “adventurers,” welcomed by guild staff portraying characters of different races and personalities. Through immersive settings, character-driven interactions, themed food and drinks, quests, and other interactive experiences, guests are invited to embark on a fantasy journey of their own.
+The café also features a stage and sound system, hosting occasional performances, fan gatherings, and themed events. Its otherworldly menu ranges from the “Flame-Seared General Orc Rice Bowl,” inspired by the triumph over a formidable foe, to “Kiss of the Minotaur,” a beef tongue dish inspired by the legendary creature, alongside a variety of fantasy-themed creations.
+At Isekaicafe Ungetsu, each visit is designed to be more than a meal—it is a brief passage into another world, where every guest can leave with an adventure story of their own.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1373,16 +1395,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1391,7 +1413,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -1402,40 +1424,40 @@
     </row>
     <row r="2" spans="1:13" ht="264">
       <c r="A2" s="2" t="s">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>156</v>
+        <v>146</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E2" s="9" t="s">
+        <v>143</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="E2" s="9" t="s">
-        <v>153</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="I2" s="6" t="s">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>149</v>
+        <v>139</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>148</v>
+        <v>138</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>147</v>
+        <v>137</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>10</v>
@@ -1443,38 +1465,38 @@
     </row>
     <row r="3" spans="1:13" ht="264">
       <c r="A3" s="2" t="s">
-        <v>146</v>
+        <v>136</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>145</v>
+        <v>135</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>144</v>
+        <v>134</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>143</v>
+        <v>133</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>142</v>
+        <v>132</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>141</v>
+        <v>131</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="6" t="s">
-        <v>139</v>
+        <v>129</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>138</v>
+        <v>128</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>137</v>
+        <v>127</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>136</v>
+        <v>126</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>10</v>
@@ -1482,40 +1504,40 @@
     </row>
     <row r="4" spans="1:13" ht="264">
       <c r="A4" s="2" t="s">
-        <v>135</v>
+        <v>125</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>134</v>
+        <v>124</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>133</v>
+        <v>123</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>10</v>
@@ -1523,79 +1545,79 @@
     </row>
     <row r="5" spans="1:13" ht="231">
       <c r="A5" s="2" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="6" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="280.5">
+    <row r="6" spans="1:13" ht="330">
       <c r="A6" s="2" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="K6" s="11" t="s">
-        <v>106</v>
+        <v>170</v>
       </c>
       <c r="L6" s="5" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>10</v>
@@ -1603,38 +1625,38 @@
     </row>
     <row r="7" spans="1:13" ht="409.5">
       <c r="A7" s="2" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>103</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>99</v>
+        <v>91</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>98</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="13" t="s">
-        <v>97</v>
+        <v>89</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>159</v>
+        <v>149</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>161</v>
+        <v>151</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>10</v>
@@ -1642,38 +1664,38 @@
     </row>
     <row r="8" spans="1:13" ht="280.5">
       <c r="A8" s="2" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="13" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>10</v>
@@ -1681,40 +1703,40 @@
     </row>
     <row r="9" spans="1:13" ht="247.5">
       <c r="A9" s="2" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>10</v>
@@ -1722,38 +1744,38 @@
     </row>
     <row r="10" spans="1:13" ht="264">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="13" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>10</v>
@@ -1761,38 +1783,38 @@
     </row>
     <row r="11" spans="1:13" ht="297">
       <c r="A11" s="2" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="13" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>10</v>
@@ -1839,16 +1861,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1857,7 +1879,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -1866,42 +1888,42 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="280.5">
+    <row r="2" spans="1:13" ht="363">
       <c r="A2" s="2" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>14</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>161</v>
+      </c>
+      <c r="I2" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="G2" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="J2" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>17</v>
-      </c>
       <c r="K2" s="11" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>10</v>
@@ -1912,37 +1934,37 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>156</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>24</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>51</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>25</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>10</v>
@@ -1953,68 +1975,74 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>29</v>
-      </c>
       <c r="G4" s="12" t="s">
-        <v>48</v>
+        <v>41</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="7" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:13" ht="115.5">
+    <row r="5" spans="1:13" ht="396">
       <c r="A5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>163</v>
       </c>
       <c r="C5" t="s">
-        <v>32</v>
+        <v>164</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>20</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>43</v>
+        <v>36</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>34</v>
+        <v>165</v>
       </c>
       <c r="G5" s="12" t="s">
-        <v>49</v>
+        <v>168</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="7" t="s">
-        <v>36</v>
+        <v>32</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>167</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>38</v>
+        <v>162</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>12</v>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4665C514-1209-43BD-9324-6F755CB18A91}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1381778-DD22-4941-AA7F-CA9D3F1F1013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="藝術入店" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
   <si>
     <t>id</t>
   </si>
@@ -74,9 +74,6 @@
   </si>
   <si>
     <t>shop-02</t>
-  </si>
-  <si>
-    <t>無</t>
   </si>
   <si>
     <t>shop-03</t>
@@ -1395,16 +1392,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1413,7 +1410,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -1424,40 +1421,40 @@
     </row>
     <row r="2" spans="1:13" ht="264">
       <c r="A2" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="E2" s="9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K2" s="11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>10</v>
@@ -1465,38 +1462,38 @@
     </row>
     <row r="3" spans="1:13" ht="264">
       <c r="A3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E3" s="9" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="6" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="K3" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>10</v>
@@ -1504,40 +1501,40 @@
     </row>
     <row r="4" spans="1:13" ht="264">
       <c r="A4" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B4" s="14" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E4" s="10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>10</v>
@@ -1545,38 +1542,38 @@
     </row>
     <row r="5" spans="1:13" ht="231">
       <c r="A5" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="E5" s="10" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H5" s="2"/>
       <c r="I5" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>10</v>
@@ -1584,40 +1581,40 @@
     </row>
     <row r="6" spans="1:13" ht="330">
       <c r="A6" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E6" s="10" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="K6" s="11" t="s">
         <v>169</v>
       </c>
-      <c r="K6" s="11" t="s">
-        <v>170</v>
-      </c>
       <c r="L6" s="5" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>10</v>
@@ -1625,38 +1622,38 @@
     </row>
     <row r="7" spans="1:13" ht="409.5">
       <c r="A7" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H7" s="2"/>
       <c r="I7" s="13" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="K7" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="L7" s="5" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M7" s="2" t="s">
         <v>10</v>
@@ -1664,38 +1661,38 @@
     </row>
     <row r="8" spans="1:13" ht="280.5">
       <c r="A8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="H8" s="2"/>
       <c r="I8" s="13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="K8" s="11" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="L8" s="5" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="M8" s="2" t="s">
         <v>10</v>
@@ -1703,40 +1700,40 @@
     </row>
     <row r="9" spans="1:13" ht="247.5">
       <c r="A9" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="K9" s="11" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="L9" s="5" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="M9" s="2" t="s">
         <v>10</v>
@@ -1744,38 +1741,38 @@
     </row>
     <row r="10" spans="1:13" ht="264">
       <c r="A10" s="2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H10" s="2"/>
       <c r="I10" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="K10" s="11" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="L10" s="5" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="M10" s="2" t="s">
         <v>10</v>
@@ -1783,38 +1780,38 @@
     </row>
     <row r="11" spans="1:13" ht="297">
       <c r="A11" s="2" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="H11" s="2"/>
       <c r="I11" s="13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="K11" s="11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L11" s="5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>10</v>
@@ -1861,16 +1858,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1879,7 +1876,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -1893,37 +1890,37 @@
         <v>9</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" s="12" t="s">
+        <v>159</v>
+      </c>
+      <c r="H2" s="12" t="s">
+        <v>160</v>
+      </c>
+      <c r="I2" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>161</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>15</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>10</v>
@@ -1934,37 +1931,37 @@
         <v>11</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="E3" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E3" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="H3" s="12" t="s">
+        <v>155</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="G3" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="H3" s="12" t="s">
-        <v>156</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="J3" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="L3" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="K3" s="11" t="s">
-        <v>43</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>10</v>
@@ -1972,38 +1969,38 @@
     </row>
     <row r="4" spans="1:13" ht="297">
       <c r="A4" s="2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E4" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>28</v>
-      </c>
       <c r="G4" s="12" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="H4" s="12"/>
       <c r="I4" s="7" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="K4" s="11" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="L4" s="5" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>10</v>
@@ -2011,41 +2008,41 @@
     </row>
     <row r="5" spans="1:13" ht="396">
       <c r="A5" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B5" t="s">
+        <v>162</v>
+      </c>
+      <c r="C5" t="s">
         <v>163</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="10" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>165</v>
-      </c>
       <c r="G5" s="12" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H5" s="12"/>
       <c r="I5" s="7" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J5" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="K5" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>167</v>
-      </c>
       <c r="L5" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:13">

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1381778-DD22-4941-AA7F-CA9D3F1F1013}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36F4FB3-5331-4417-A495-427EDAA5DB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="2835" yWindow="1845" windowWidth="28740" windowHeight="19065" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="藝術入店" sheetId="2" r:id="rId1"/>
     <sheet name="合作店家" sheetId="1" r:id="rId2"/>
+    <sheet name="合作項目" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -38,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="170">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="211">
   <si>
     <t>id</t>
   </si>
@@ -600,35 +601,6 @@
   </si>
   <si>
     <t>Miss Coffee Bar</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>覓’</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="Arial"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">s </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <rFont val="微軟正黑體"/>
-        <family val="2"/>
-        <charset val="136"/>
-      </rPr>
-      <t>咖啡小酒館</t>
-    </r>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -887,11 +859,441 @@
 At Isekaicafe Ungetsu, each visit is designed to be more than a meal—it is a brief passage into another world, where every guest can leave with an adventure story of their own.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>覓’s 咖啡小酒館</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作項目</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>無</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>缺</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>有</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>partnership-01</t>
+  </si>
+  <si>
+    <t>partnership-02</t>
+  </si>
+  <si>
+    <t>partnership-03</t>
+  </si>
+  <si>
+    <t>partnership-04</t>
+  </si>
+  <si>
+    <t>partnership-05</t>
+  </si>
+  <si>
+    <t>partnership-06</t>
+  </si>
+  <si>
+    <t>partnership-07</t>
+  </si>
+  <si>
+    <t>partnership-08</t>
+  </si>
+  <si>
+    <t>partnership-09</t>
+  </si>
+  <si>
+    <t>partnership-10</t>
+  </si>
+  <si>
+    <t>partnership-11</t>
+  </si>
+  <si>
+    <t>Mirror of Erised
+Vodka / Green Tea / Jasmine / Rose / Longan / Smoke
+以綠茶為基底，揉合茉莉與玫瑰的細緻花香，搭配煙燻龍眼的果香與燻香，呈現清雅卻帶有朦朧層次的風味。
+如同「灰色自動體」對感知的重新編碼，將自然的香氣拆解、轉化，再重新組合成一種介於熟悉與陌生之間的感官體驗。銀白色的酒體，也象徵著訊息經過運算後所留下的中性介面。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>商品介紹</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror of Erised
+Vodka / Green Tea / Jasmine / Rose / Longan / Smoke</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>項目英文</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《在記憶折返以前》-響應展覽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《起 · 初》-黑白麻糬組合禮盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>售價</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>起・初 四入限定盒  NT$100
+起・初 八入限定盒  NT$180</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>配合臺北數位藝術節展期，推出期間限定黑白麻糬組合。
+夜・黑芝麻｜晝・白椰子
+從黑夜到白晝，都是祝福。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>常態販售</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜四入盒	NT$90
+麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜八入盒	NT$160
+冷泡茶 500ml	撒母耳｜原味蕎麥冷泡茶	NT$65
+冷泡茶 500ml	以斯帖｜桂花蕎麥冷泡茶	NT$75
+冷泡茶 500ml	大衛｜藜麥蕎麥冷泡茶	NT$85
+咖啡	限量手沖咖啡 HOT / ICED	依現場供應與公告</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>時間</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>10/31（六）白晝之夜	特別延長營業	12:00 - 20:00
+11/01（日）	展期限定開放	14:00 - 17:00
+11/07（六）	展期限定開放	10:30 - 16:30
+11/08（日）	展期限定開放	10:30 - 16:30
+11/14（六）	展期限定開放	10:30 - 16:30
+11/15（日）	展期限定開放	10:30 - 16:30
+平日	預訂制	同一取貨日 25 盒以上可成團；至少 7 天前完成預訂
+展期週末限定 OPEN HOUSE；平日採預約制；麻糬每日限量新鮮手作，售完為止。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>展期 | 10月10日至11月8日
+開幕 | 10月17日15:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《在記憶折返以前》由台北雙人創作團體Fina與Tony共同展出。Fina以散文式數位影像收集街道、人物與生活片刻；Tony透過翻轉、鏡像與重組，將城市燈火化為影像詩。兩人的作品游移於具象與抽象之間，沿著光線、記憶與時間交會，邀請觀眾辨認那些尚未說完、仍在心中折返的感受。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰色自動體
+GRAY AUTONOMOUS ENTITY
+一杯，介於人與機器之間的灰色狀態。
+咖啡的深黑、藍莓的色彩，
+黑金竹碳將一切拉回灰階，
+再以牛奶覆上一層柔軟的白。
+像是正在生成的物件，
+沒有固定的形狀，也沒有唯一的答案。
+在黑與白之間，
+讓味覺成為另一種感知介面。
+Coffee × Blueberry × Black Gold Bamboo Charcoal × Milk
+臺北數位藝術節限定
+藝術節限定優惠 $100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《竹炭拿鐵》-特調咖啡飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOMA・VEIL</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>意指雖然無法理解、看不清本質，但能讓人穩定、安心、愉悅的魔藥（AI科技）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《墨魚披薩套餐》-披薩套餐組合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《SOMA・VEIL》-特調飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🦑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>墨魚披薩｜把整片海的鮮味，烤進一張披薩裡。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>使用新鮮墨魚囊、墨魚肉與透抽，搭配辛香料細火翻炒，再打成濃郁細緻的墨魚醬。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>不只是「黑色」而已，入口是滿滿的鮮甜海味，越吃越香。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>將墨魚醬均勻抹上披薩麵團，鋪上新鮮透抽，送進高溫窯爐烘烤。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>出爐後，再搭配酸香開胃的莎莎醬與現刨魷魚乾。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>窯烤的焦香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>墨魚的鮮甜</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>莎莎醬的酸香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> × </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>魷魚乾的鹹香</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>一口下去，海味、香氣與口感一層一層堆疊。</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>響應優惠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon花草茶
+源起於火山口下的西恩花園新鮮採摘的一杯花草茶，如同「味蕾的花束」，將山裡日月積累的感受，透過一杯花草茶帶入每個人的生活，分享大自然的美好與能量。
+CNSalon花冰菓
+以台灣豐盛的鮮果與西恩花園中自然香草氣味，化作味蕾上冰紛的夏日花園，一支冰菓、一支花，把一座花園結冰，在口中盛開！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>《CNSalon花草茶、CNSalon花冰菓》-特製飲品、冰淇淋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon Herbal Tea
+Freshly harvested from CN Garden beneath the volcanic landscape, each cup of herbal tea is like a “bouquet for the palate.” Infused with the flavors and sensations shaped by days and seasons in the mountains, the tea brings the beauty and energy of nature into everyday life, one cup at a time.
+CNSalon Floral Fruit Ice Pops
+Made with Taiwan’s abundant fresh fruits and naturally fragrant herbs from CN Garden, these ice pops transform the flavors of a summer garden into a refreshing frozen treat. A fruit ice pop, a flower—a whole garden captured in ice, blooming with every bite.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="176" formatCode="&quot;NT$&quot;#,##0_);\(&quot;NT$&quot;#,##0\)"/>
+  </numFmts>
   <fonts count="12">
     <font>
       <sz val="12"/>
@@ -918,25 +1320,11 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
-    </font>
-    <font>
       <u/>
       <sz val="12"/>
       <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
-      <charset val="136"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="新細明體"/>
-      <family val="1"/>
       <charset val="136"/>
       <scheme val="minor"/>
     </font>
@@ -960,21 +1348,38 @@
       <name val="Carlito"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <name val="新細明體"/>
-      <family val="2"/>
+      <family val="1"/>
       <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="微軟正黑體"/>
+      <color theme="1"/>
+      <name val="Segoe UI Symbol"/>
       <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="12"/>
-      <name val="Arial"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -998,12 +1403,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1013,41 +1418,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1365,20 +1779,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DD7EC979-70CF-4845-9D38-9711D9AB954A}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:N12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="7" customWidth="1"/>
-    <col min="3" max="3" width="6.25" customWidth="1"/>
+    <col min="1" max="1" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="3" max="3" width="22.75" customWidth="1"/>
     <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="7" width="20.375" customWidth="1"/>
-    <col min="8" max="8" width="10.5" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="47.25" customWidth="1"/>
-    <col min="12" max="12" width="38.375" customWidth="1"/>
+    <col min="6" max="8" width="10.5" customWidth="1"/>
+    <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="33">
+    <row r="1" spans="1:14" ht="33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1401,7 +1814,7 @@
         <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1418,410 +1831,444 @@
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="264">
-      <c r="A2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="B2" s="2" t="s">
+      <c r="N1" s="10" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="B2" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="C2" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E2" s="9" t="s">
+      <c r="D2" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="6" t="s">
         <v>141</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="F2" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="I2" s="6" t="s">
+      <c r="G2" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="H2" s="6" t="s">
+        <v>153</v>
+      </c>
+      <c r="I2" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="K2" s="11" t="s">
+      <c r="J2" s="6" t="s">
         <v>137</v>
       </c>
+      <c r="K2" s="8" t="s">
+        <v>136</v>
+      </c>
       <c r="L2" s="5" t="s">
-        <v>136</v>
-      </c>
-      <c r="M2" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="M2" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="264">
-      <c r="A3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="B3" s="2" t="s">
+      <c r="N2" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14">
+      <c r="A3" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="B3" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="C3" s="6" t="s">
         <v>132</v>
       </c>
-      <c r="E3" s="9" t="s">
+      <c r="D3" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="E3" s="6" t="s">
         <v>130</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="F3" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="H3" s="2"/>
-      <c r="I3" s="6" t="s">
+      <c r="G3" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="H3" s="6"/>
+      <c r="I3" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="J3" s="6" t="s">
         <v>126</v>
       </c>
+      <c r="K3" s="8" t="s">
+        <v>125</v>
+      </c>
       <c r="L3" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="M3" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="M3" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="264">
-      <c r="A4" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="B4" s="14" t="s">
+      <c r="N3" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="B4" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="6" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="I4" s="13" t="s">
+      <c r="H4" s="6" t="s">
+        <v>152</v>
+      </c>
+      <c r="I4" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="8" t="s">
         <v>115</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>114</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="231">
-      <c r="A5" s="2" t="s">
+      <c r="N4" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="A5" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="10" t="s">
+      <c r="E5" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="F5" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="G5" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="2"/>
-      <c r="I5" s="6" t="s">
+      <c r="H5" s="6"/>
+      <c r="I5" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="K5" s="11" t="s">
+      <c r="K5" s="8" t="s">
         <v>106</v>
       </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="M5" s="2" t="s">
+      <c r="M5" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="6" spans="1:13" ht="330">
-      <c r="A6" s="2" t="s">
+      <c r="N5" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="6" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="6" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="6" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="6" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="F6" s="6" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="G6" s="6" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I6" s="13" t="s">
+      <c r="H6" s="6" t="s">
+        <v>150</v>
+      </c>
+      <c r="I6" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="K6" s="8" t="s">
         <v>168</v>
-      </c>
-      <c r="K6" s="11" t="s">
-        <v>169</v>
       </c>
       <c r="L6" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="M6" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" ht="409.5">
-      <c r="A7" s="2" t="s">
+      <c r="N6" s="6" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="6" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="2" t="s">
+      <c r="F7" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="2" t="s">
+      <c r="G7" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="2"/>
-      <c r="I7" s="13" t="s">
+      <c r="H7" s="6"/>
+      <c r="I7" s="7" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="K7" s="11" t="s">
-        <v>150</v>
+      <c r="J7" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="K7" s="8" t="s">
+        <v>149</v>
       </c>
       <c r="L7" s="5" t="s">
         <v>87</v>
       </c>
-      <c r="M7" s="2" t="s">
+      <c r="M7" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" ht="280.5">
-      <c r="A8" s="2" t="s">
+      <c r="N7" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="A8" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="6" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="10" t="s">
+      <c r="E8" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="F8" s="6" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="2" t="s">
+      <c r="G8" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="2"/>
-      <c r="I8" s="13" t="s">
+      <c r="H8" s="6"/>
+      <c r="I8" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="6" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="11" t="s">
-        <v>149</v>
+      <c r="K8" s="8" t="s">
+        <v>148</v>
       </c>
       <c r="L8" s="5" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="M8" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="247.5">
-      <c r="A9" s="2" t="s">
+      <c r="N8" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="A9" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="10" t="s">
+      <c r="E9" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="2" t="s">
+      <c r="F9" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="2" t="s">
+      <c r="G9" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I9" s="13" t="s">
+      <c r="H9" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="I9" s="7" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="11" t="s">
+      <c r="K9" s="8" t="s">
         <v>67</v>
       </c>
       <c r="L9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="M9" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" ht="264">
-      <c r="A10" s="2" t="s">
+      <c r="N9" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="A10" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="6" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="6" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="10" t="s">
+      <c r="E10" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="2" t="s">
+      <c r="F10" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="2" t="s">
+      <c r="G10" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="2"/>
-      <c r="I10" s="13" t="s">
+      <c r="H10" s="6"/>
+      <c r="I10" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="11" t="s">
+      <c r="K10" s="8" t="s">
         <v>56</v>
       </c>
       <c r="L10" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="M10" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" ht="297">
-      <c r="A11" s="2" t="s">
+      <c r="N10" s="6" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="A11" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="10" t="s">
+      <c r="E11" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="2" t="s">
+      <c r="F11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="2" t="s">
+      <c r="G11" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="2"/>
-      <c r="I11" s="13" t="s">
+      <c r="H11" s="6"/>
+      <c r="I11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="6" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="8" t="s">
         <v>45</v>
       </c>
       <c r="L11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="M11" s="6" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="N11" s="6" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="B12" s="2"/>
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
+      <c r="N12" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -1832,19 +2279,20 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F597B7B-DB6F-4918-AACF-F2DE3E6BF4FC}">
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
-    <col min="2" max="2" width="6.25" customWidth="1"/>
-    <col min="3" max="3" width="7.25" customWidth="1"/>
-    <col min="6" max="7" width="20.375" customWidth="1"/>
+    <col min="1" max="1" width="6.375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="17.5" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="6" max="7" width="11.375" customWidth="1"/>
     <col min="8" max="8" width="10.875" customWidth="1"/>
-    <col min="9" max="9" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="47.25" customWidth="1"/>
-    <col min="12" max="12" width="38.375" customWidth="1"/>
+    <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.5" customWidth="1"/>
+    <col min="12" max="12" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="33">
+    <row r="1" spans="1:14" ht="33">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1867,7 +2315,7 @@
         <v>37</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -1884,172 +2332,436 @@
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:13" ht="363">
-      <c r="A2" s="2" t="s">
+      <c r="N1" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14" s="16" customFormat="1" ht="14.25">
+      <c r="A2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="11" t="s">
+        <v>13</v>
+      </c>
+      <c r="E2" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="G2" s="13" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" s="13" t="s">
+        <v>159</v>
+      </c>
+      <c r="I2" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="J2" s="4" t="s">
+        <v>15</v>
+      </c>
+      <c r="K2" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="L2" s="4" t="s">
         <v>156</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="G2" s="12" t="s">
-        <v>159</v>
-      </c>
-      <c r="H2" s="12" t="s">
-        <v>160</v>
-      </c>
-      <c r="I2" s="6" t="s">
-        <v>14</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="11" t="s">
-        <v>41</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="M2" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="3" spans="1:13" ht="247.5">
-      <c r="A3" s="2" t="s">
+      <c r="N2" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:14" s="16" customFormat="1" ht="14.25">
+      <c r="A3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="12" t="s">
+      <c r="G3" s="13" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="12" t="s">
-        <v>155</v>
-      </c>
-      <c r="I3" s="6" t="s">
+      <c r="H3" s="13" t="s">
+        <v>154</v>
+      </c>
+      <c r="I3" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="J3" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="11" t="s">
+      <c r="K3" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="2" t="s">
+      <c r="L3" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="M3" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="4" spans="1:13" ht="297">
-      <c r="A4" s="2" t="s">
+      <c r="N3" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" s="16" customFormat="1" ht="14.25">
+      <c r="A4" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="F4" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="12" t="s">
+      <c r="G4" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="12"/>
-      <c r="I4" s="7" t="s">
+      <c r="H4" s="13"/>
+      <c r="I4" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="11" t="s">
+      <c r="K4" s="15" t="s">
         <v>43</v>
       </c>
       <c r="L4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="2" t="s">
+      <c r="M4" s="4" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="5" spans="1:13" ht="396">
-      <c r="A5" s="2" t="s">
+      <c r="N4" s="16" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14" s="16" customFormat="1" ht="14.25">
+      <c r="A5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="C5" t="s">
+      <c r="D5" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E5" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="13" t="s">
+        <v>166</v>
+      </c>
+      <c r="H5" s="13"/>
+      <c r="I5" s="17" t="s">
+        <v>31</v>
+      </c>
+      <c r="J5" s="4" t="s">
         <v>164</v>
       </c>
-      <c r="G5" s="12" t="s">
-        <v>167</v>
-      </c>
-      <c r="H5" s="12"/>
-      <c r="I5" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="4" t="s">
         <v>165</v>
       </c>
-      <c r="K5" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="L5" s="2" t="s">
+      <c r="L5" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="A6" s="2"/>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="A7" s="2"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1A3856-7136-49AB-BF44-6D141EF36F56}">
+  <dimension ref="A1:L12"/>
+  <sheetFormatPr defaultRowHeight="16.5"/>
+  <cols>
+    <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
+    <col min="2" max="5" width="22" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="10" width="22" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>196</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>194</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="10"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" t="s">
+        <v>174</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="3"/>
+      <c r="F2" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" t="s">
+        <v>175</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="F3" s="3"/>
+      <c r="G3" s="3" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" t="s">
+        <v>177</v>
+      </c>
+      <c r="B5" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="M5" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="2"/>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="2"/>
+      <c r="C5" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" t="s">
+        <v>178</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="3" t="s">
+        <v>208</v>
+      </c>
+      <c r="H6" s="3" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" t="s">
+        <v>179</v>
+      </c>
+      <c r="B7" s="9" t="s">
+        <v>169</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>122</v>
+      </c>
+      <c r="D7" t="s">
+        <v>201</v>
+      </c>
+      <c r="F7" s="12">
+        <v>100</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" t="s">
+        <v>180</v>
+      </c>
+      <c r="B8" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="D9" t="s">
+        <v>205</v>
+      </c>
+      <c r="E9" t="s">
+        <v>202</v>
+      </c>
+      <c r="G9" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17.25">
+      <c r="A10" t="s">
+        <v>182</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>85</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" t="s">
+        <v>183</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>53</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="D12" t="s">
+        <v>207</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C36F4FB3-5331-4417-A495-427EDAA5DB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C68699D-9DBB-445F-AFC7-D86B0BA98B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2835" yWindow="1845" windowWidth="28740" windowHeight="19065" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="藝術入店" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="283" uniqueCount="211">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="228">
   <si>
     <t>id</t>
   </si>
@@ -924,20 +924,7 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Mirror of Erised
-Vodka / Green Tea / Jasmine / Rose / Longan / Smoke</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>項目英文</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《在記憶折返以前》-響應展覽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《起 · 初》-黑白麻糬組合禮盒</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1009,23 +996,11 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《竹炭拿鐵》-特調咖啡飲品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>SOMA・VEIL</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
     <t>意指雖然無法理解、看不清本質，但能讓人穩定、安心、愉悅的魔藥（AI科技）</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《墨魚披薩套餐》-披薩套餐組合</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《SOMA・VEIL》-特調飲品</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1276,14 +1251,163 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>《CNSalon花草茶、CNSalon花冰菓》-特製飲品、冰淇淋</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNSalon Herbal Tea
 Freshly harvested from CN Garden beneath the volcanic landscape, each cup of herbal tea is like a “bouquet for the palate.” Infused with the flavors and sensations shaped by days and seasons in the mountains, the tea brings the beauty and energy of nature into everyday life, one cup at a time.
 CNSalon Floral Fruit Ice Pops
 Made with Taiwan’s abundant fresh fruits and naturally fragrant herbs from CN Garden, these ice pops transform the flavors of a summer garden into a refreshing frozen treat. A fruit ice pop, a flower—a whole garden captured in ice, blooming with every bite.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror of Erised</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作種類</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑白麻糬組合禮盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>起 · 初</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>響應展覽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在記憶折返以前</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon花草茶、CNSalon花冰菓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特製餐點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特調飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特調咖啡飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹炭拿鐵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>披薩套餐組合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨魚披薩套餐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon Herbal Tea, CNSalon Floral Fruit Ice Pops</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before Memory Turns Back</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>In celebration of the Taipei Digital Art Festival, a limited-edition black-and-white mochi set will be available exclusively during the festival period.
+Night · Black Sesame | Day · White Coconut
+From night to day, each one carries a blessing.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror of Erised
+Vodka / Green Tea / Jasmine / Rose / Longan / Smoke
+Built on a green tea base, this cocktail layers the delicate floral notes of jasmine and rose with the fruity aroma and smoky depth of smoked longan, creating an elegant yet subtly hazy flavor profile.
+Echoing Gray Autonomous Entity and its reconfiguration of perception, natural aromas are deconstructed, transformed, and recombined into a sensory experience that exists somewhere between the familiar and the unfamiliar. The silvery-white appearance of the cocktail evokes a neutral interface—the residue of information after it has been processed and recomposed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before Memory Turns Back is a joint exhibition by Taipei-based artist duo Fina and Tony. Fina gathers fragments of streets, people, and everyday life through essayistic digital imagery, while Tony transforms the lights of the city into visual poetry through inversion, mirroring, and recomposition.
+Moving between the figurative and the abstract, their works trace intersections of light, memory, and time, inviting viewers to recognize feelings that remain unfinished and continue to return within.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRAY AUTONOMOUS ENTITY
+A drink suspended in the gray area between human and machine.
+The deep black of coffee and the color of blueberry are drawn back into grayscale by black gold bamboo charcoal, before being covered with a soft layer of white milk.
+Like an object still in the process of becoming, it has no fixed form and no single answer.
+Between black and white, taste becomes another interface for perception.
+Coffee × Blueberry × Black Gold Bamboo Charcoal × Milk
+Taipei Digital Art Festival Exclusive
+Festival Special | NT$100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A potion that may be impossible to fully understand or see for what it truly is, yet brings a sense of stability, reassurance, and pleasure—a metaphor for AI technology.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🦑</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Squid Ink Pizza | The flavors of the sea, baked into every slice.
+Fresh squid ink, cuttlefish, and squid are slowly sautéed with aromatic spices, then blended into a rich, velvety squid ink sauce.
+More than just its striking black appearance, this pizza is packed with the natural sweetness and umami of the sea. The squid ink sauce is spread generously over the pizza dough, topped with fresh squid, and baked at high heat in the oven.
+Once out of the oven, it is finished with bright, tangy salsa and freshly shaved dried squid.
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>🔥</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Charred oven-baked aroma × Sweet ocean flavors × Tangy salsa × Savory dried squid
+With every bite, layers of seafood flavor, aroma, and texture unfold one after another.</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bamboo Charcoal Latte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Squid Ink Pizza Set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Origin · Beginning</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2292,7 +2416,7 @@
     <col min="12" max="12" width="22.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33">
+    <row r="1" spans="1:14" ht="49.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2523,16 +2647,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1A3856-7136-49AB-BF44-6D141EF36F56}">
-  <dimension ref="A1:L12"/>
+  <dimension ref="A1:M12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="22" customWidth="1"/>
-    <col min="6" max="6" width="27" customWidth="1"/>
-    <col min="7" max="10" width="22" customWidth="1"/>
+    <col min="2" max="6" width="22" customWidth="1"/>
+    <col min="7" max="7" width="27" customWidth="1"/>
+    <col min="8" max="11" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2546,29 +2670,32 @@
         <v>170</v>
       </c>
       <c r="E1" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="H1" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>193</v>
+      </c>
+      <c r="K1" s="1" t="s">
         <v>191</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>196</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="L1" s="10"/>
-    </row>
-    <row r="2" spans="1:12">
+      <c r="M1" s="10"/>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
         <v>174</v>
       </c>
@@ -2579,26 +2706,34 @@
         <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>227</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="E2" s="3"/>
-      <c r="F2" s="3" t="s">
+      <c r="I2" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="K2" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="G2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>197</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
         <v>175</v>
       </c>
@@ -2609,17 +2744,26 @@
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F3" s="3"/>
-      <c r="G3" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="G3" s="3"/>
+      <c r="H3" s="3" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="4" spans="1:12">
+      <c r="I3" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>176</v>
       </c>
@@ -2629,8 +2773,11 @@
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="5" spans="1:12">
+      <c r="L4" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>177</v>
       </c>
@@ -2641,16 +2788,28 @@
         <v>162</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>199</v>
+        <v>209</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" t="s">
+        <v>208</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>196</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12">
+        <v>221</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>178</v>
       </c>
@@ -2661,16 +2820,25 @@
         <v>132</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="3" t="s">
-        <v>208</v>
+        <v>210</v>
+      </c>
+      <c r="E6" t="s">
+        <v>217</v>
+      </c>
+      <c r="F6" t="s">
+        <v>211</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>210</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12">
+        <v>202</v>
+      </c>
+      <c r="I6" s="3" t="s">
+        <v>203</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>179</v>
       </c>
@@ -2681,16 +2849,28 @@
         <v>122</v>
       </c>
       <c r="D7" t="s">
-        <v>201</v>
-      </c>
-      <c r="F7" s="12">
+        <v>214</v>
+      </c>
+      <c r="E7" t="s">
+        <v>225</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" s="12">
         <v>100</v>
       </c>
-      <c r="G7" s="3" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12">
+      <c r="H7" s="3" t="s">
+        <v>197</v>
+      </c>
+      <c r="I7" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>180</v>
       </c>
@@ -2700,8 +2880,11 @@
       <c r="C8" s="6" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="9" spans="1:12">
+      <c r="L8" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>181</v>
       </c>
@@ -2712,16 +2895,25 @@
         <v>102</v>
       </c>
       <c r="D9" t="s">
-        <v>205</v>
+        <v>198</v>
       </c>
       <c r="E9" t="s">
-        <v>202</v>
-      </c>
-      <c r="G9" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="17.25">
+        <v>198</v>
+      </c>
+      <c r="F9" t="s">
+        <v>212</v>
+      </c>
+      <c r="H9" t="s">
+        <v>199</v>
+      </c>
+      <c r="I9" t="s">
+        <v>223</v>
+      </c>
+      <c r="L9" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="17.25">
       <c r="A10" t="s">
         <v>182</v>
       </c>
@@ -2732,13 +2924,25 @@
         <v>84</v>
       </c>
       <c r="D10" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" s="3" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12">
+        <v>216</v>
+      </c>
+      <c r="E10" t="s">
+        <v>226</v>
+      </c>
+      <c r="F10" t="s">
+        <v>215</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="I10" s="3" t="s">
+        <v>224</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>183</v>
       </c>
@@ -2748,8 +2952,11 @@
       <c r="C11" s="6" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="12" spans="1:12">
+      <c r="L11" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>184</v>
       </c>
@@ -2759,8 +2966,11 @@
       <c r="C12" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="D12" t="s">
-        <v>207</v>
+      <c r="F12" t="s">
+        <v>201</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>171</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C68699D-9DBB-445F-AFC7-D86B0BA98B17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B2494F-5CD3-4241-A8F7-1CA381E5C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="藝術入店" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="228">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="230">
   <si>
     <t>id</t>
   </si>
@@ -1408,6 +1408,14 @@
   </si>
   <si>
     <t>Origin · Beginning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No. 188, Sec. 3, Chengde Rd., Datong Dist., Taipei City 103034, Taiwan (R.O.C.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市大同區承德路三段188號</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2545,7 +2553,7 @@
         <v>10</v>
       </c>
       <c r="N3" s="4" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:14" s="16" customFormat="1" ht="14.25">
@@ -2601,10 +2609,10 @@
         <v>162</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>19</v>
+        <v>229</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>35</v>
+        <v>228</v>
       </c>
       <c r="F5" s="4" t="s">
         <v>163</v>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{88B2494F-5CD3-4241-A8F7-1CA381E5C8B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFBDAA9-144C-4B5D-BFA5-C4FB41B76CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
   <sheets>
     <sheet name="藝術入店" sheetId="2" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="312" uniqueCount="230">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="235">
   <si>
     <t>id</t>
   </si>
@@ -896,9 +896,6 @@
   </si>
   <si>
     <t>partnership-06</t>
-  </si>
-  <si>
-    <t>partnership-07</t>
   </si>
   <si>
     <t>partnership-08</t>
@@ -1004,9 +1001,140 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
+    <t>響應優惠</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon花草茶
+源起於火山口下的西恩花園新鮮採摘的一杯花草茶，如同「味蕾的花束」，將山裡日月積累的感受，透過一杯花草茶帶入每個人的生活，分享大自然的美好與能量。
+CNSalon花冰菓
+以台灣豐盛的鮮果與西恩花園中自然香草氣味，化作味蕾上冰紛的夏日花園，一支冰菓、一支花，把一座花園結冰，在口中盛開！</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon Herbal Tea
+Freshly harvested from CN Garden beneath the volcanic landscape, each cup of herbal tea is like a “bouquet for the palate.” Infused with the flavors and sensations shaped by days and seasons in the mountains, the tea brings the beauty and energy of nature into everyday life, one cup at a time.
+CNSalon Floral Fruit Ice Pops
+Made with Taiwan’s abundant fresh fruits and naturally fragrant herbs from CN Garden, these ice pops transform the flavors of a summer garden into a refreshing frozen treat. A fruit ice pop, a flower—a whole garden captured in ice, blooming with every bite.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror of Erised</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>合作種類</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑白麻糬組合禮盒</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>起 · 初</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>響應展覽</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>在記憶折返以前</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon花草茶、CNSalon花冰菓</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特製餐點</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特調飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特調咖啡飲品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>竹炭拿鐵</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>披薩套餐組合</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>墨魚披薩套餐</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon Herbal Tea, CNSalon Floral Fruit Ice Pops</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before Memory Turns Back</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>In celebration of the Taipei Digital Art Festival, a limited-edition black-and-white mochi set will be available exclusively during the festival period.
+Night · Black Sesame | Day · White Coconut
+From night to day, each one carries a blessing.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Mirror of Erised
+Vodka / Green Tea / Jasmine / Rose / Longan / Smoke
+Built on a green tea base, this cocktail layers the delicate floral notes of jasmine and rose with the fruity aroma and smoky depth of smoked longan, creating an elegant yet subtly hazy flavor profile.
+Echoing Gray Autonomous Entity and its reconfiguration of perception, natural aromas are deconstructed, transformed, and recombined into a sensory experience that exists somewhere between the familiar and the unfamiliar. The silvery-white appearance of the cocktail evokes a neutral interface—the residue of information after it has been processed and recomposed.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Before Memory Turns Back is a joint exhibition by Taipei-based artist duo Fina and Tony. Fina gathers fragments of streets, people, and everyday life through essayistic digital imagery, while Tony transforms the lights of the city into visual poetry through inversion, mirroring, and recomposition.
+Moving between the figurative and the abstract, their works trace intersections of light, memory, and time, inviting viewers to recognize feelings that remain unfinished and continue to return within.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRAY AUTONOMOUS ENTITY
+A drink suspended in the gray area between human and machine.
+The deep black of coffee and the color of blueberry are drawn back into grayscale by black gold bamboo charcoal, before being covered with a soft layer of white milk.
+Like an object still in the process of becoming, it has no fixed form and no single answer.
+Between black and white, taste becomes another interface for perception.
+Coffee × Blueberry × Black Gold Bamboo Charcoal × Milk
+Taipei Digital Art Festival Exclusive
+Festival Special | NT$100</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A potion that may be impossible to fully understand or see for what it truly is, yet brings a sense of stability, reassurance, and pleasure—a metaphor for AI technology.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bamboo Charcoal Latte</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Squid Ink Pizza Set</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Origin · Beginning</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>No. 188, Sec. 3, Chengde Rd., Datong Dist., Taipei City 103034, Taiwan (R.O.C.)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>台北市大同區承德路三段188號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -1015,7 +1143,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1024,7 +1152,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1035,7 +1163,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1045,7 +1173,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1056,7 +1184,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1066,7 +1194,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1077,7 +1205,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1087,7 +1215,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1098,7 +1226,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1108,7 +1236,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1119,7 +1247,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1129,7 +1257,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -1138,7 +1266,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1147,7 +1275,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1158,7 +1286,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1167,7 +1295,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1178,7 +1306,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1187,7 +1315,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1198,7 +1326,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1207,7 +1335,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1218,7 +1346,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
@@ -1228,7 +1356,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1240,120 +1368,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>響應優惠</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNSalon花草茶
-源起於火山口下的西恩花園新鮮採摘的一杯花草茶，如同「味蕾的花束」，將山裡日月積累的感受，透過一杯花草茶帶入每個人的生活，分享大自然的美好與能量。
-CNSalon花冰菓
-以台灣豐盛的鮮果與西恩花園中自然香草氣味，化作味蕾上冰紛的夏日花園，一支冰菓、一支花，把一座花園結冰，在口中盛開！</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNSalon Herbal Tea
-Freshly harvested from CN Garden beneath the volcanic landscape, each cup of herbal tea is like a “bouquet for the palate.” Infused with the flavors and sensations shaped by days and seasons in the mountains, the tea brings the beauty and energy of nature into everyday life, one cup at a time.
-CNSalon Floral Fruit Ice Pops
-Made with Taiwan’s abundant fresh fruits and naturally fragrant herbs from CN Garden, these ice pops transform the flavors of a summer garden into a refreshing frozen treat. A fruit ice pop, a flower—a whole garden captured in ice, blooming with every bite.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mirror of Erised</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>合作種類</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>黑白麻糬組合禮盒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>起 · 初</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>響應展覽</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>在記憶折返以前</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNSalon花草茶、CNSalon花冰菓</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>特製餐點</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>特調飲品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>特調咖啡飲品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>竹炭拿鐵</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>披薩套餐組合</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>墨魚披薩套餐</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNSalon Herbal Tea, CNSalon Floral Fruit Ice Pops</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Before Memory Turns Back</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>In celebration of the Taipei Digital Art Festival, a limited-edition black-and-white mochi set will be available exclusively during the festival period.
-Night · Black Sesame | Day · White Coconut
-From night to day, each one carries a blessing.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Mirror of Erised
-Vodka / Green Tea / Jasmine / Rose / Longan / Smoke
-Built on a green tea base, this cocktail layers the delicate floral notes of jasmine and rose with the fruity aroma and smoky depth of smoked longan, creating an elegant yet subtly hazy flavor profile.
-Echoing Gray Autonomous Entity and its reconfiguration of perception, natural aromas are deconstructed, transformed, and recombined into a sensory experience that exists somewhere between the familiar and the unfamiliar. The silvery-white appearance of the cocktail evokes a neutral interface—the residue of information after it has been processed and recomposed.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Before Memory Turns Back is a joint exhibition by Taipei-based artist duo Fina and Tony. Fina gathers fragments of streets, people, and everyday life through essayistic digital imagery, while Tony transforms the lights of the city into visual poetry through inversion, mirroring, and recomposition.
-Moving between the figurative and the abstract, their works trace intersections of light, memory, and time, inviting viewers to recognize feelings that remain unfinished and continue to return within.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>GRAY AUTONOMOUS ENTITY
-A drink suspended in the gray area between human and machine.
-The deep black of coffee and the color of blueberry are drawn back into grayscale by black gold bamboo charcoal, before being covered with a soft layer of white milk.
-Like an object still in the process of becoming, it has no fixed form and no single answer.
-Between black and white, taste becomes another interface for perception.
-Coffee × Blueberry × Black Gold Bamboo Charcoal × Milk
-Taipei Digital Art Festival Exclusive
-Festival Special | NT$100</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>A potion that may be impossible to fully understand or see for what it truly is, yet brings a sense of stability, reassurance, and pleasure—a metaphor for AI technology.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -1362,7 +1379,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1377,7 +1394,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Segoe UI Symbol"/>
         <family val="2"/>
@@ -1386,7 +1403,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="新細明體"/>
         <family val="2"/>
@@ -1399,23 +1416,47 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>Bamboo Charcoal Latte</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Squid Ink Pizza Set</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Origin · Beginning</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>No. 188, Sec. 3, Chengde Rd., Datong Dist., Taipei City 103034, Taiwan (R.O.C.)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>台北市大同區承德路三段188號</t>
+    <t>黑炭法式牛軋餅</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>歐華酒店 × 臺北數位藝術節｜限定黑炭法式牛軋餅
+灰色，不只是另一種顏色
+當機器越來越懂得模仿人，
+人與機器之間的界線，又在哪裡？
+呼應2026臺北數位藝術節對科技、創作與人文之間關係的探索，歐華酒店以熟悉的法式牛軋餅為創作載體，推出限定黑炭法式牛軋餅。
+這一次，我們刻意讓它與傳統牛軋餅的繽紛色彩形成對比，將一場關於「人」與「機器」的思考，藏進一份可以品嚐的甜點裡。
+繽紛的法式牛軋餅，象徵人的色彩——有溫度、有情緒，也保留著手作創作的不規則與獨特。
+而這一次，歐華酒店以黑炭為靈感，將法式牛軋餅化作一抹深灰。精準、純粹、近乎一致的色彩，彷彿來自數位世界的產物，讓「人」與「機器」之間的界線，成為一場味覺與視覺的想像。法式甜點的細緻工藝，遇上黑炭獨有的自然深色，將法式風格與東方元素融入一口牛軋餅。
+當機器開始能創造影像、文字與藝術，什麼樣的色彩，仍然只屬於人？
+繽紛，是人的色彩。
+灰色，是機器的想像。
+而你，看見的是什麼？</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特製點心</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>partnership-07</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Charcoal French Nougat Cracker</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>The Riviera Hotel × Taipei Digital Art Festival | Limited-Edition Charcoal French Nougat Cracker
+Gray is more than just another color.
+As machines become increasingly capable of imitating humans, where does the boundary between human and machine lie?
+Echoing the 2026 Taipei Digital Art Festival’s exploration of the relationships between technology, creativity, and humanity, The Riviera Hotel reimagines its familiar French nougat cracker as a limited-edition charcoal creation. In deliberate contrast to the vibrant colors of traditional nougat crackers, this version transforms a reflection on “humans” and “machines” into something that can be tasted.
+The colorful French nougat cracker represents the colors of humanity—warm, emotional, and marked by the irregularity and individuality of something made by hand.
+For this special edition, The Riviera Hotel draws inspiration from charcoal, transforming the French nougat cracker into a deep shade of gray. Its precise, pure, almost uniform appearance evokes an object from the digital world, turning the boundary between “human” and “machine” into an exploration of both taste and vision. Refined French pastry craftsmanship meets the naturally deep tones of charcoal, bringing French style and Eastern elements together in a single bite.
+As machines begin to create images, words, and art, what colors still belong uniquely to us?
+Color is human.
+Gray is the imagination of the machine.
+What do you see?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1426,7 +1467,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="&quot;NT$&quot;#,##0_);\(&quot;NT$&quot;#,##0\)"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1495,23 +1536,32 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Segoe UI Symbol"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="新細明體"/>
-      <family val="1"/>
-      <charset val="136"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1550,9 +1600,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1577,9 +1624,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1592,7 +1636,13 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1963,435 +2013,435 @@
       <c r="M1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="N1" s="10" t="s">
+      <c r="N1" s="9" t="s">
         <v>170</v>
       </c>
     </row>
     <row r="2" spans="1:14">
-      <c r="A2" s="6" t="s">
+      <c r="A2" s="5" t="s">
         <v>145</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>142</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="5" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="I2" s="7" t="s">
+      <c r="I2" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="J2" s="6" t="s">
+      <c r="J2" s="5" t="s">
         <v>137</v>
       </c>
-      <c r="K2" s="8" t="s">
+      <c r="K2" s="7" t="s">
         <v>136</v>
       </c>
-      <c r="L2" s="5" t="s">
+      <c r="L2" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="M2" s="6" t="s">
+      <c r="M2" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="6" t="s">
+      <c r="N2" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:14">
-      <c r="A3" s="6" t="s">
+      <c r="A3" s="5" t="s">
         <v>134</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>131</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="H3" s="6"/>
-      <c r="I3" s="7" t="s">
+      <c r="H3" s="5"/>
+      <c r="I3" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="K3" s="8" t="s">
+      <c r="K3" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="L3" s="5" t="s">
+      <c r="L3" s="4" t="s">
         <v>124</v>
       </c>
-      <c r="M3" s="6" t="s">
+      <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="6" t="s">
+      <c r="N3" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:14">
-      <c r="A4" s="6" t="s">
+      <c r="A4" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="F4" s="6" t="s">
+      <c r="F4" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="H4" s="6" t="s">
+      <c r="H4" s="5" t="s">
         <v>152</v>
       </c>
-      <c r="I4" s="7" t="s">
+      <c r="I4" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="J4" s="6" t="s">
+      <c r="J4" s="5" t="s">
         <v>116</v>
       </c>
-      <c r="K4" s="8" t="s">
+      <c r="K4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="M4" s="6" t="s">
+      <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="6" t="s">
+      <c r="N4" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:14">
-      <c r="A5" s="6" t="s">
+      <c r="A5" s="5" t="s">
         <v>113</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="5" t="s">
         <v>111</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="5" t="s">
         <v>109</v>
       </c>
-      <c r="F5" s="6" t="s">
+      <c r="F5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H5" s="6"/>
-      <c r="I5" s="7" t="s">
+      <c r="H5" s="5"/>
+      <c r="I5" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="J5" s="6" t="s">
+      <c r="J5" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="K5" s="8" t="s">
+      <c r="K5" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="L5" s="6" t="s">
+      <c r="L5" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="M5" s="6" t="s">
+      <c r="M5" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="6" t="s">
-        <v>172</v>
+      <c r="N5" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:14">
-      <c r="A6" s="6" t="s">
+      <c r="A6" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="F6" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="H6" s="6" t="s">
+      <c r="H6" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="I6" s="7" t="s">
+      <c r="I6" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="J6" s="6" t="s">
+      <c r="J6" s="5" t="s">
         <v>167</v>
       </c>
-      <c r="K6" s="8" t="s">
+      <c r="K6" s="7" t="s">
         <v>168</v>
       </c>
-      <c r="L6" s="5" t="s">
+      <c r="L6" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="M6" s="6" t="s">
+      <c r="M6" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N6" s="6" t="s">
+      <c r="N6" s="5" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:14">
-      <c r="A7" s="6" t="s">
+      <c r="A7" s="5" t="s">
         <v>95</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>93</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="5" t="s">
         <v>91</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="5" t="s">
         <v>89</v>
       </c>
-      <c r="H7" s="6"/>
-      <c r="I7" s="7" t="s">
+      <c r="H7" s="5"/>
+      <c r="I7" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="J7" s="6" t="s">
+      <c r="J7" s="5" t="s">
         <v>147</v>
       </c>
-      <c r="K7" s="8" t="s">
+      <c r="K7" s="7" t="s">
         <v>149</v>
       </c>
-      <c r="L7" s="5" t="s">
+      <c r="L7" s="4" t="s">
         <v>87</v>
       </c>
-      <c r="M7" s="6" t="s">
+      <c r="M7" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N7" s="6" t="s">
+      <c r="N7" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="8" spans="1:14">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="5" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="H8" s="6"/>
-      <c r="I8" s="7" t="s">
+      <c r="H8" s="5"/>
+      <c r="I8" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="J8" s="6" t="s">
+      <c r="J8" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="K8" s="8" t="s">
+      <c r="K8" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="L8" s="5" t="s">
+      <c r="L8" s="4" t="s">
         <v>77</v>
       </c>
-      <c r="M8" s="6" t="s">
+      <c r="M8" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N8" s="6" t="s">
+      <c r="N8" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="9" spans="1:14">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="5" t="s">
         <v>151</v>
       </c>
-      <c r="I9" s="7" t="s">
+      <c r="I9" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="J9" s="6" t="s">
+      <c r="J9" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="K9" s="8" t="s">
+      <c r="K9" s="7" t="s">
         <v>67</v>
       </c>
-      <c r="L9" s="5" t="s">
+      <c r="L9" s="4" t="s">
         <v>66</v>
       </c>
-      <c r="M9" s="6" t="s">
+      <c r="M9" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N9" s="6" t="s">
+      <c r="N9" s="5" t="s">
         <v>172</v>
       </c>
     </row>
     <row r="10" spans="1:14">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="H10" s="6"/>
-      <c r="I10" s="7" t="s">
+      <c r="H10" s="5"/>
+      <c r="I10" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="J10" s="6" t="s">
+      <c r="J10" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="K10" s="8" t="s">
+      <c r="K10" s="7" t="s">
         <v>56</v>
       </c>
-      <c r="L10" s="5" t="s">
+      <c r="L10" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="M10" s="6" t="s">
+      <c r="M10" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N10" s="6" t="s">
+      <c r="N10" s="5" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:14">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H11" s="6"/>
-      <c r="I11" s="7" t="s">
+      <c r="H11" s="5"/>
+      <c r="I11" s="6" t="s">
         <v>47</v>
       </c>
-      <c r="J11" s="6" t="s">
+      <c r="J11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="K11" s="8" t="s">
+      <c r="K11" s="7" t="s">
         <v>45</v>
       </c>
-      <c r="L11" s="5" t="s">
+      <c r="L11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="M11" s="6" t="s">
+      <c r="M11" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="N11" s="6" t="s">
+      <c r="N11" s="5" t="s">
         <v>172</v>
       </c>
     </row>
@@ -2400,7 +2450,7 @@
       <c r="C12" s="2"/>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="N12" s="6"/>
+      <c r="N12" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2468,175 +2518,175 @@
         <v>170</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="16" customFormat="1" ht="14.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:14" s="14" customFormat="1" ht="14.25">
+      <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11" t="s">
+      <c r="D2" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="11" t="s">
+      <c r="E2" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="G2" s="13" t="s">
+      <c r="G2" s="11" t="s">
         <v>158</v>
       </c>
-      <c r="H2" s="13" t="s">
+      <c r="H2" s="11" t="s">
         <v>159</v>
       </c>
-      <c r="I2" s="14" t="s">
+      <c r="I2" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="4" t="s">
+      <c r="J2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="K2" s="15" t="s">
+      <c r="K2" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="L2" s="4" t="s">
+      <c r="L2" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="M2" s="4" t="s">
+      <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N2" s="4" t="s">
+      <c r="N2" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="16" customFormat="1" ht="14.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:14" s="14" customFormat="1" ht="14.25">
+      <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="11" t="s">
         <v>154</v>
       </c>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J3" s="4" t="s">
+      <c r="J3" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="K3" s="15" t="s">
+      <c r="K3" s="13" t="s">
         <v>42</v>
       </c>
-      <c r="L3" s="4" t="s">
+      <c r="L3" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="4" t="s">
+      <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N3" s="4" t="s">
+      <c r="N3" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="16" customFormat="1" ht="14.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:14" s="14" customFormat="1" ht="14.25">
+      <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="13" t="s">
+      <c r="G4" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="H4" s="13"/>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="11"/>
+      <c r="I4" s="15" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="K4" s="15" t="s">
+      <c r="K4" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="L4" s="5" t="s">
+      <c r="L4" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="M4" s="4" t="s">
+      <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="16" t="s">
+      <c r="N4" s="14" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="16" customFormat="1" ht="14.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:14" s="14" customFormat="1" ht="14.25">
+      <c r="A5" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="E5" s="4" t="s">
-        <v>228</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="D5" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>163</v>
       </c>
-      <c r="G5" s="13" t="s">
+      <c r="G5" s="11" t="s">
         <v>166</v>
       </c>
-      <c r="H5" s="13"/>
-      <c r="I5" s="17" t="s">
+      <c r="H5" s="11"/>
+      <c r="I5" s="15" t="s">
         <v>31</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="L5" s="4" t="s">
+      <c r="L5" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="M5" s="4" t="s">
+      <c r="M5" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N5" s="4" t="s">
+      <c r="N5" s="3" t="s">
         <v>173</v>
       </c>
     </row>
@@ -2665,46 +2715,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="16" t="s">
+        <v>186</v>
+      </c>
+      <c r="F1" s="16" t="s">
+        <v>203</v>
+      </c>
+      <c r="G1" s="16" t="s">
         <v>187</v>
       </c>
-      <c r="F1" s="1" t="s">
-        <v>205</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>186</v>
-      </c>
-      <c r="I1" s="1" t="s">
+      <c r="H1" s="16" t="s">
+        <v>185</v>
+      </c>
+      <c r="I1" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="J1" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>191</v>
-      </c>
-      <c r="L1" s="1" t="s">
+      <c r="J1" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="M1" s="10"/>
+      <c r="M1" s="9"/>
     </row>
     <row r="2" spans="1:13">
-      <c r="A2" t="s">
+      <c r="A2" s="14" t="s">
         <v>174</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -2714,35 +2764,35 @@
         <v>16</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="G2" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="H2" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="H2" s="3" t="s">
-        <v>190</v>
-      </c>
       <c r="I2" s="3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="3" spans="1:13">
-      <c r="A3" t="s">
+      <c r="A3" s="14" t="s">
         <v>175</v>
       </c>
       <c r="B3" s="3" t="s">
@@ -2752,27 +2802,29 @@
         <v>18</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>218</v>
+      </c>
+      <c r="J3" s="14"/>
+      <c r="K3" s="14"/>
       <c r="L3" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="4" spans="1:13">
-      <c r="A4" t="s">
+      <c r="A4" s="14" t="s">
         <v>176</v>
       </c>
       <c r="B4" s="3" t="s">
@@ -2781,12 +2833,20 @@
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
+      <c r="D4" s="14"/>
+      <c r="E4" s="14"/>
+      <c r="F4" s="14"/>
+      <c r="G4" s="14"/>
+      <c r="H4" s="14"/>
+      <c r="I4" s="14"/>
+      <c r="J4" s="14"/>
+      <c r="K4" s="14"/>
       <c r="L4" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="5" spans="1:13">
-      <c r="A5" t="s">
+      <c r="A5" s="14" t="s">
         <v>177</v>
       </c>
       <c r="B5" s="3" t="s">
@@ -2796,187 +2856,233 @@
         <v>162</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="F5" t="s">
-        <v>208</v>
-      </c>
+        <v>216</v>
+      </c>
+      <c r="F5" s="14" t="s">
+        <v>206</v>
+      </c>
+      <c r="G5" s="14"/>
       <c r="H5" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>195</v>
-      </c>
+        <v>194</v>
+      </c>
+      <c r="K5" s="14"/>
       <c r="L5" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="6" spans="1:13">
-      <c r="A6" t="s">
+      <c r="A6" s="14" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>132</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="E6" t="s">
-        <v>217</v>
-      </c>
-      <c r="F6" t="s">
-        <v>211</v>
-      </c>
+        <v>208</v>
+      </c>
+      <c r="E6" s="14" t="s">
+        <v>215</v>
+      </c>
+      <c r="F6" s="14" t="s">
+        <v>209</v>
+      </c>
+      <c r="G6" s="14"/>
       <c r="H6" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>203</v>
-      </c>
+        <v>201</v>
+      </c>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
       <c r="L6" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="7" spans="1:13">
-      <c r="A7" t="s">
+      <c r="A7" s="14" t="s">
         <v>179</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>169</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="D7" t="s">
-        <v>214</v>
-      </c>
-      <c r="E7" t="s">
-        <v>225</v>
-      </c>
-      <c r="F7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" s="12">
+      <c r="D7" s="14" t="s">
+        <v>212</v>
+      </c>
+      <c r="E7" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="F7" s="14" t="s">
+        <v>211</v>
+      </c>
+      <c r="G7" s="17">
         <v>100</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>222</v>
-      </c>
+        <v>220</v>
+      </c>
+      <c r="J7" s="14"/>
+      <c r="K7" s="14"/>
       <c r="L7" s="3" t="s">
         <v>173</v>
       </c>
     </row>
     <row r="8" spans="1:13">
-      <c r="A8" t="s">
-        <v>180</v>
-      </c>
-      <c r="B8" s="6" t="s">
+      <c r="A8" s="14" t="s">
+        <v>232</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>112</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="D8" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="G8" s="3"/>
+      <c r="H8" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="J8" s="14"/>
+      <c r="K8" s="14"/>
       <c r="L8" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
     </row>
     <row r="9" spans="1:13">
-      <c r="A9" t="s">
-        <v>181</v>
-      </c>
-      <c r="B9" s="6" t="s">
+      <c r="A9" s="14" t="s">
+        <v>180</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>103</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="14" t="s">
+        <v>197</v>
+      </c>
+      <c r="F9" s="14" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" s="14"/>
+      <c r="H9" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="E9" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" t="s">
-        <v>212</v>
-      </c>
-      <c r="H9" t="s">
-        <v>199</v>
-      </c>
-      <c r="I9" t="s">
-        <v>223</v>
-      </c>
+      <c r="I9" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
       <c r="L9" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="17.25">
-      <c r="A10" t="s">
-        <v>182</v>
-      </c>
-      <c r="B10" s="6" t="s">
+    <row r="10" spans="1:13">
+      <c r="A10" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B10" s="5" t="s">
         <v>85</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="D10" t="s">
-        <v>216</v>
-      </c>
-      <c r="E10" t="s">
-        <v>226</v>
-      </c>
-      <c r="F10" t="s">
-        <v>215</v>
-      </c>
+      <c r="D10" s="14" t="s">
+        <v>214</v>
+      </c>
+      <c r="E10" s="14" t="s">
+        <v>223</v>
+      </c>
+      <c r="F10" s="14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" s="14"/>
       <c r="H10" s="3" t="s">
-        <v>200</v>
+        <v>227</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>228</v>
+      </c>
+      <c r="J10" s="14"/>
+      <c r="K10" s="14"/>
       <c r="L10" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="11" spans="1:13">
-      <c r="A11" t="s">
-        <v>183</v>
-      </c>
-      <c r="B11" s="6" t="s">
+      <c r="A11" s="14" t="s">
+        <v>182</v>
+      </c>
+      <c r="B11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="5" t="s">
         <v>74</v>
       </c>
+      <c r="D11" s="14"/>
+      <c r="E11" s="14"/>
+      <c r="F11" s="14"/>
+      <c r="G11" s="14"/>
+      <c r="H11" s="14"/>
+      <c r="I11" s="14"/>
+      <c r="J11" s="14"/>
+      <c r="K11" s="14"/>
       <c r="L11" s="3" t="s">
         <v>171</v>
       </c>
     </row>
     <row r="12" spans="1:13">
-      <c r="A12" t="s">
-        <v>184</v>
-      </c>
-      <c r="B12" s="6" t="s">
+      <c r="A12" s="14" t="s">
+        <v>183</v>
+      </c>
+      <c r="B12" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C12" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="F12" t="s">
-        <v>201</v>
-      </c>
+      <c r="D12" s="14"/>
+      <c r="E12" s="14"/>
+      <c r="F12" s="14" t="s">
+        <v>199</v>
+      </c>
+      <c r="G12" s="14"/>
+      <c r="H12" s="14"/>
+      <c r="I12" s="14"/>
+      <c r="J12" s="14"/>
+      <c r="K12" s="14"/>
       <c r="L12" s="3" t="s">
         <v>171</v>
       </c>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEFBDAA9-144C-4B5D-BFA5-C4FB41B76CB5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB009834-6166-4820-A31D-8FA8521CE2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="235">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="239">
   <si>
     <t>id</t>
   </si>
@@ -78,9 +78,6 @@
   </si>
   <si>
     <t>shop-03</t>
-  </si>
-  <si>
-    <t>臺北市中山區新庄里吉林路456巷10號</t>
   </si>
   <si>
     <t>02-25957137</t>
@@ -89,10 +86,6 @@
   <si>
     <t>三樓家以馬內利食研室，藏身於吉林路巷弄，是揉合手作飲食、咖啡、設計及生活美學的複合式空間。店內以純手工麻糬為核心，將約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜等口味賦予不同故事與祝福，另外也提供無咖啡因冷泡蕎麥茶及自家烘焙手沖咖啡，讓每一位顧客體驗手作的溫度。
 空間亦結合「攝設的，強尼小姐」設計工作室，從食物、包裝到視覺創作，傳遞「每一口，都是一點療癒」的品牌理念，將日常飲食轉變為可分享的溫度與祝福。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>emhanuel</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -461,10 +454,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>TAIPEI FLORIST</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>台北花苑</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -653,10 +642,6 @@
   </si>
   <si>
     <t>CNSalon</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>CNSalon 花草茶店</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -810,14 +795,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t xml:space="preserve">Gallery 188（杉畝藝術有限公司、OhMyDeer Floral） </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">Gallery 188（Sam’s Art Co. 、OhMyDeer Floral） </t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>周六  13:00-18:00
 周日  13:00-18:00
 平日 | 預約參觀
@@ -886,12 +863,6 @@
     <t>partnership-02</t>
   </si>
   <si>
-    <t>partnership-03</t>
-  </si>
-  <si>
-    <t>partnership-04</t>
-  </si>
-  <si>
     <t>partnership-05</t>
   </si>
   <si>
@@ -925,31 +896,9 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>售價</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>起・初 四入限定盒  NT$100
-起・初 八入限定盒  NT$180</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>配合臺北數位藝術節展期，推出期間限定黑白麻糬組合。
 夜・黑芝麻｜晝・白椰子
 從黑夜到白晝，都是祝福。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>常態販售</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜四入盒	NT$90
-麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜八入盒	NT$160
-冷泡茶 500ml	撒母耳｜原味蕎麥冷泡茶	NT$65
-冷泡茶 500ml	以斯帖｜桂花蕎麥冷泡茶	NT$75
-冷泡茶 500ml	大衛｜藜麥蕎麥冷泡茶	NT$85
-咖啡	限量手沖咖啡 HOT / ICED	依現場供應與公告</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -965,15 +914,6 @@
 11/15（日）	展期限定開放	10:30 - 16:30
 平日	預訂制	同一取貨日 25 盒以上可成團；至少 7 天前完成預訂
 展期週末限定 OPEN HOUSE；平日採預約制；麻糬每日限量新鮮手作，售完為止。</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>展期 | 10月10日至11月8日
-開幕 | 10月17日15:00</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>《在記憶折返以前》由台北雙人創作團體Fina與Tony共同展出。Fina以散文式數位影像收集街道、人物與生活片刻；Tony透過翻轉、鏡像與重組，將城市燈火化為影像詩。兩人的作品游移於具象與抽象之間，沿著光線、記憶與時間交會，邀請觀眾辨認那些尚未說完、仍在心中折返的感受。</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1027,10 +967,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>黑白麻糬組合禮盒</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>起 · 初</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -1056,10 +992,6 @@
   </si>
   <si>
     <t>特調咖啡飲品</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>竹炭拿鐵</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1089,11 +1021,6 @@
 Vodka / Green Tea / Jasmine / Rose / Longan / Smoke
 Built on a green tea base, this cocktail layers the delicate floral notes of jasmine and rose with the fruity aroma and smoky depth of smoked longan, creating an elegant yet subtly hazy flavor profile.
 Echoing Gray Autonomous Entity and its reconfiguration of perception, natural aromas are deconstructed, transformed, and recombined into a sensory experience that exists somewhere between the familiar and the unfamiliar. The silvery-white appearance of the cocktail evokes a neutral interface—the residue of information after it has been processed and recomposed.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Before Memory Turns Back is a joint exhibition by Taipei-based artist duo Fina and Tony. Fina gathers fragments of streets, people, and everyday life through essayistic digital imagery, while Tony transforms the lights of the city into visual poetry through inversion, mirroring, and recomposition.
-Moving between the figurative and the abstract, their works trace intersections of light, memory, and time, inviting viewers to recognize feelings that remain unfinished and continue to return within.</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1109,10 +1036,6 @@
   </si>
   <si>
     <t>A potion that may be impossible to fully understand or see for what it truly is, yet brings a sense of stability, reassurance, and pleasure—a metaphor for AI technology.</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Bamboo Charcoal Latte</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1459,15 +1382,231 @@
 What do you see?</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>臺北市中山區新庄里吉林路456巷10號</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CNSalon 火山口下的花茶店</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>拿掉</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>—以父芝名—</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>向經典調酒「Godfather 教父」致敬，以威士忌與杏仁酒構築深沉而溫潤的酒體，覆上灰色芝麻冰淇淋。黑芝麻的濃厚堅果香與酒液交疊，如同在灰色世界裡運行的一段未知程式。沒有絕對的黑，也沒有純粹的白，只有不斷變化的灰階。以「灰色自動體」為題，將熟悉的味覺重新拆解、重組，讓冰淇淋、酒與記憶，在夜色中形成新的感官語言。</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>partnership-03</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>黑白麻糬組合禮盒 四入/八入</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>供應商品</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">
+限定販售
+起・初 四入限定盒 
+起・初 八入限定盒 
+常態販售
+麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜四入盒
+麻糬	原本四款：約瑟花生、路得黑芝麻、約拿紅豆、彼得酸菜｜八入盒
+冷泡茶 500ml	撒母耳｜原味蕎麥冷泡茶
+冷泡茶 500ml	以斯帖｜桂花蕎麥冷泡茶
+冷泡茶 500ml	大衛｜藜麥蕎麥冷泡茶
+咖啡	限量手沖咖啡 HOT / ICED</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>3F. Lovelove</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Taipei Florist</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">Gallery 188
+杉畝藝術有限公司
+OhMyDeer Floral </t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Gallery 188
+Sam’s Art Co.
+OhMyDeer Floral</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>灰色自動體</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>GRAY AUTONOMOUS ENTITY</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>A tribute to the classic cocktail Godfather, this creation brings together whisky and amaretto to form a deep yet mellow base, topped with gray sesame gelato.
+The rich, nutty aroma of black sesame intertwines with the spirits like an unknown program running through a world of gray. There is no absolute black, nor pure white—only an ever-shifting spectrum of gray.
+Inspired by Gray Autonomous Entity, familiar flavors are deconstructed and recomposed, allowing gelato, spirits, and memory to form a new sensory language in the night.</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>-In the Name of the Father-</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>杉畝藝術Galler 188</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+誠摯邀請</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+《在記憶折返以前》
+Fina × Tony 雙個展
+記憶在影像裡留下切面，也在光線、反射與觀看者的移動之間，再次改變方向。
+本展集結數位影像、複合媒材裝置與現場互動。Fina以散文式影像記錄當代生活，讓過去、現在與尚未抵達的自己在同一空間相遇；Tony則以影像詩折疊城市、光與記憶，在具象與抽象之間留下持續迴盪的感受。
+配合台北數位藝術節與白晝之夜活動，現場備有酒水與小點。邀請你來看展、喝一杯、與藝術家聊聊，並透過「記憶折返卡」留下一段想再次回到的時間。
+活動免費，請由此報名：
+https://docs.google.com/forms/d/1Am6vOhdfdfXUUZrtqZQOAk4P3on8OBo0ywA7KPN8F1o/viewform</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>zh
+▍展期
+2026.10.10 Sat. — 11.08 Sun.
+▍開幕
+2026.10.17 Sat. 15:00–18:00
+▍折返的記憶之夜
+2026.10.31 Sat. 18:00–21:00
+en
+▍Exhibition Period  
+Oct. 10 (Sat) – Nov. 8 (Sun), 2026
+▍Opening Reception  
+Oct. 17 (Sat), 2026  
+15:00–18:00
+▍A Night of Returning Memories
+Oct. 31 (Sat), 2026  
+18:00–21:00</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Gallery 188 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">  
+Cordially Invites You </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI Symbol"/>
+        <family val="2"/>
+      </rPr>
+      <t>✦</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="新細明體"/>
+        <family val="2"/>
+        <charset val="136"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+"Before Memory Turns Back"
+Fina × Tony Duo Exhibition
+Memory leaves its traces in images, shifting direction once again through light, reflection, and the movement of the viewer.
+Bringing together digital imagery, mixed-media installations, and interactive experiences, the exhibition explores the shifting relationship between memory, perception, and time. Fina documents contemporary life through essayistic imagery, allowing the past, the present, and versions of the self yet to come to meet within the same space. Tony folds together the city, light, and memory through visual poetry, leaving lingering sensations that move between the figurative and the abstract.
+Presented in conjunction with the Taipei Digital Art Festival and Nuit Blanche Taipei, the evening will feature drinks and light refreshments. Come see the exhibition, enjoy a drink, and chat with the artists. You are also invited to leave behind a moment you would like to return to through the “Memory Return Card.”
+Admission is free. Please register here:
+https://docs.google.com/forms/d/1Am6vOhdfdfXUUZrtqZQOAk4P3on8OBo0ywA7KPN8F1o/viewform</t>
+    </r>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>partnership-04</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>特製冰淇淋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="176" formatCode="&quot;NT$&quot;#,##0_);\(&quot;NT$&quot;#,##0\)"/>
-  </numFmts>
-  <fonts count="13">
+  <fonts count="12">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1500,13 +1639,6 @@
       <family val="2"/>
       <charset val="136"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="微軟正黑體"/>
-      <family val="2"/>
-      <charset val="136"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1588,7 +1720,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
@@ -1600,49 +1732,49 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1965,10 +2097,13 @@
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.875" customWidth="1"/>
+    <col min="2" max="2" width="25.375" customWidth="1"/>
     <col min="3" max="3" width="22.75" customWidth="1"/>
-    <col min="4" max="5" width="9" customWidth="1"/>
-    <col min="6" max="8" width="10.5" customWidth="1"/>
+    <col min="4" max="4" width="35.125" customWidth="1"/>
+    <col min="5" max="5" width="58.875" customWidth="1"/>
+    <col min="6" max="6" width="39.25" customWidth="1"/>
+    <col min="7" max="7" width="24.375" customWidth="1"/>
+    <col min="8" max="8" width="32.625" customWidth="1"/>
     <col min="9" max="9" width="9.75" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="23.375" customWidth="1"/>
   </cols>
@@ -1987,16 +2122,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2005,7 +2140,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -2014,435 +2149,435 @@
         <v>8</v>
       </c>
       <c r="N1" s="9" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="5" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>144</v>
+        <v>140</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="E2" s="5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="I2" s="6" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="K2" s="7" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="L2" s="4" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="M2" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="3" spans="1:14">
       <c r="A3" s="5" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>133</v>
+        <v>218</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="E3" s="5" t="s">
-        <v>130</v>
+        <v>127</v>
       </c>
       <c r="F3" s="5" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="G3" s="5" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="6" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="K3" s="7" t="s">
-        <v>125</v>
+        <v>122</v>
       </c>
       <c r="L3" s="4" t="s">
-        <v>124</v>
+        <v>121</v>
       </c>
       <c r="M3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" s="5" t="s">
-        <v>123</v>
+        <v>120</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>169</v>
+        <v>163</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D4" s="5" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="F4" s="5" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
       <c r="G4" s="5" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="H4" s="5" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="I4" s="6" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="J4" s="5" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="K4" s="7" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="L4" s="4" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
       <c r="M4" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N4" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="5" spans="1:14">
       <c r="A5" s="5" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="D5" s="5" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="E5" s="5" t="s">
-        <v>109</v>
+        <v>106</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G5" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="6" t="s">
-        <v>108</v>
+        <v>105</v>
       </c>
       <c r="J5" s="5" t="s">
-        <v>107</v>
+        <v>104</v>
       </c>
       <c r="K5" s="7" t="s">
-        <v>106</v>
+        <v>103</v>
       </c>
       <c r="L5" s="5" t="s">
-        <v>105</v>
+        <v>102</v>
       </c>
       <c r="M5" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:14">
       <c r="A6" s="5" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="D6" s="5" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="E6" s="5" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="G6" s="5" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="H6" s="5" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="J6" s="5" t="s">
-        <v>167</v>
+        <v>161</v>
       </c>
       <c r="K6" s="7" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="L6" s="4" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="M6" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N6" s="5" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="7" spans="1:14">
       <c r="A7" s="5" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>93</v>
+        <v>227</v>
       </c>
       <c r="D7" s="5" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E7" s="5" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="G7" s="5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="J7" s="5" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="K7" s="7" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="L7" s="4" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="M7" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N7" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="8" spans="1:14">
       <c r="A8" s="5" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D8" s="5" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E8" s="5" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="G8" s="5" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="J8" s="5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="K8" s="7" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="L8" s="4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="M8" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N8" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:14">
       <c r="A9" s="5" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D9" s="5" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="E9" s="5" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="F9" s="5" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="G9" s="5" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="H9" s="5" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="J9" s="5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="K9" s="7" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="L9" s="4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="M9" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N9" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="10" spans="1:14">
       <c r="A10" s="5" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C10" s="5" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="D10" s="5" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="E10" s="5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F10" s="5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="G10" s="5" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="J10" s="5" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="L10" s="4" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="M10" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N10" s="5" t="s">
-        <v>171</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:14">
       <c r="A11" s="5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C11" s="5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D11" s="5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E11" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="F11" s="5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="J11" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="K11" s="7" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="L11" s="4" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="M11" s="5" t="s">
         <v>10</v>
       </c>
       <c r="N11" s="5" t="s">
-        <v>172</v>
+        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -2467,7 +2602,9 @@
     <col min="1" max="1" width="6.375" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="17.5" customWidth="1"/>
     <col min="3" max="3" width="10.625" customWidth="1"/>
-    <col min="6" max="7" width="11.375" customWidth="1"/>
+    <col min="4" max="4" width="33.75" customWidth="1"/>
+    <col min="6" max="6" width="66.75" customWidth="1"/>
+    <col min="7" max="7" width="38.125" customWidth="1"/>
     <col min="8" max="8" width="10.875" customWidth="1"/>
     <col min="9" max="9" width="9.5" bestFit="1" customWidth="1"/>
     <col min="10" max="11" width="11.5" customWidth="1"/>
@@ -2488,16 +2625,16 @@
         <v>3</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F1" s="1" t="s">
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="I1" s="1" t="s">
         <v>5</v>
@@ -2506,7 +2643,7 @@
         <v>6</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="L1" s="1" t="s">
         <v>7</v>
@@ -2515,179 +2652,179 @@
         <v>8</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>170</v>
+        <v>164</v>
       </c>
     </row>
-    <row r="2" spans="1:14" s="14" customFormat="1" ht="14.25">
+    <row r="2" spans="1:14" s="13" customFormat="1" ht="156.75">
       <c r="A2" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="G2" s="16" t="s">
+        <v>154</v>
+      </c>
+      <c r="H2" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="10" t="s">
+      <c r="I2" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="E2" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="G2" s="11" t="s">
-        <v>158</v>
-      </c>
-      <c r="H2" s="11" t="s">
-        <v>159</v>
-      </c>
-      <c r="I2" s="12" t="s">
+      <c r="J2" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="J2" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="K2" s="13" t="s">
-        <v>41</v>
+      <c r="K2" s="12" t="s">
+        <v>39</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="M2" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="3" spans="1:14" s="14" customFormat="1" ht="14.25">
+    <row r="3" spans="1:14" s="13" customFormat="1" ht="14.25">
       <c r="A3" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="E3" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="F3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="G3" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="H3" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="I3" s="11" t="s">
         <v>19</v>
       </c>
-      <c r="E3" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="F3" s="3" t="s">
+      <c r="J3" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G3" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="H3" s="11" t="s">
-        <v>154</v>
-      </c>
-      <c r="I3" s="12" t="s">
+      <c r="K3" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="L3" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K3" s="13" t="s">
-        <v>42</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>23</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:14" s="14" customFormat="1" ht="14.25">
+    <row r="4" spans="1:14" s="13" customFormat="1" ht="14.25">
       <c r="A4" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="3" t="s">
+      <c r="G4" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="H4" s="10"/>
+      <c r="I4" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="E4" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="J4" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="11" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="11"/>
-      <c r="I4" s="15" t="s">
+      <c r="K4" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="L4" s="4" t="s">
         <v>30</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="K4" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" s="4" t="s">
-        <v>32</v>
       </c>
       <c r="M4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="N4" s="14" t="s">
-        <v>172</v>
+      <c r="N4" s="13" t="s">
+        <v>166</v>
       </c>
     </row>
-    <row r="5" spans="1:14" s="14" customFormat="1" ht="14.25">
+    <row r="5" spans="1:14" s="13" customFormat="1" ht="14.25">
       <c r="A5" s="3" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>161</v>
+        <v>228</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>162</v>
+        <v>229</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>226</v>
+        <v>208</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>225</v>
+        <v>207</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="G5" s="11" t="s">
-        <v>166</v>
-      </c>
-      <c r="H5" s="11"/>
-      <c r="I5" s="15" t="s">
-        <v>31</v>
+        <v>157</v>
+      </c>
+      <c r="G5" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="H5" s="10"/>
+      <c r="I5" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>164</v>
+        <v>158</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>165</v>
+        <v>159</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="M5" s="3" t="s">
         <v>10</v>
       </c>
       <c r="N5" s="3" t="s">
-        <v>173</v>
+        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -2705,386 +2842,379 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FB1A3856-7136-49AB-BF44-6D141EF36F56}">
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:L12"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="13.125" bestFit="1" customWidth="1"/>
-    <col min="2" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="27" customWidth="1"/>
-    <col min="8" max="11" width="22" customWidth="1"/>
+    <col min="2" max="10" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
-      <c r="A1" s="16" t="s">
+    <row r="1" spans="1:12">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="E1" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>189</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>224</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="L1" s="9"/>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2" s="13" t="s">
+        <v>168</v>
+      </c>
+      <c r="B2" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>223</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>201</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>225</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12">
+      <c r="A3" s="13" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12">
+      <c r="A4" s="13" t="s">
+        <v>222</v>
+      </c>
+      <c r="B4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12">
+      <c r="A5" s="13" t="s">
+        <v>237</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>200</v>
+      </c>
+      <c r="F5" s="13" t="s">
+        <v>191</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>234</v>
+      </c>
+      <c r="H5" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="I5" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="J5" s="13"/>
+      <c r="K5" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12">
+      <c r="A6" s="13" t="s">
         <v>170</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="B6" s="5" t="s">
+        <v>218</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="E6" s="13" t="s">
+        <v>199</v>
+      </c>
+      <c r="F6" s="13" t="s">
+        <v>194</v>
+      </c>
+      <c r="G6" s="3" t="s">
         <v>186</v>
       </c>
-      <c r="F1" s="16" t="s">
+      <c r="H6" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="I6" s="13"/>
+      <c r="J6" s="13"/>
+      <c r="K6" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12">
+      <c r="A7" s="13" t="s">
+        <v>171</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>163</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="D7" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="E7" s="13" t="s">
+        <v>231</v>
+      </c>
+      <c r="F7" s="13" t="s">
+        <v>196</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H7" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="G1" s="16" t="s">
-        <v>187</v>
-      </c>
-      <c r="H1" s="16" t="s">
+      <c r="I7" s="13"/>
+      <c r="J7" s="13"/>
+      <c r="K7" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="13" t="s">
+        <v>214</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>215</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="I8" s="13"/>
+      <c r="J8" s="13"/>
+      <c r="K8" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12">
+      <c r="A9" s="13" t="s">
+        <v>172</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>100</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="D9" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>183</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>195</v>
+      </c>
+      <c r="G9" s="13" t="s">
+        <v>184</v>
+      </c>
+      <c r="H9" s="13" t="s">
+        <v>204</v>
+      </c>
+      <c r="I9" s="13"/>
+      <c r="J9" s="13"/>
+      <c r="K9" s="3" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12">
+      <c r="A10" s="13" t="s">
+        <v>173</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>83</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D10" s="13" t="s">
+        <v>198</v>
+      </c>
+      <c r="E10" s="13" t="s">
+        <v>205</v>
+      </c>
+      <c r="F10" s="13" t="s">
+        <v>197</v>
+      </c>
+      <c r="G10" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="H10" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="I10" s="13"/>
+      <c r="J10" s="13"/>
+      <c r="K10" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12">
+      <c r="A11" s="13" t="s">
+        <v>174</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>72</v>
+      </c>
+      <c r="D11" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="E11" s="17" t="s">
+        <v>233</v>
+      </c>
+      <c r="F11" s="13" t="s">
+        <v>238</v>
+      </c>
+      <c r="G11" s="13" t="s">
+        <v>221</v>
+      </c>
+      <c r="H11" s="3" t="s">
+        <v>232</v>
+      </c>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12">
+      <c r="A12" s="13" t="s">
+        <v>175</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="16" t="s">
-        <v>38</v>
-      </c>
-      <c r="J1" s="16" t="s">
-        <v>192</v>
-      </c>
-      <c r="K1" s="16" t="s">
-        <v>190</v>
-      </c>
-      <c r="L1" s="16" t="s">
-        <v>8</v>
-      </c>
-      <c r="M1" s="9"/>
-    </row>
-    <row r="2" spans="1:13">
-      <c r="A2" s="14" t="s">
-        <v>174</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>224</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>204</v>
-      </c>
-      <c r="G2" s="3" t="s">
-        <v>188</v>
-      </c>
-      <c r="H2" s="3" t="s">
-        <v>189</v>
-      </c>
-      <c r="I2" s="3" t="s">
-        <v>217</v>
-      </c>
-      <c r="J2" s="3" t="s">
-        <v>193</v>
-      </c>
-      <c r="K2" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="L2" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13">
-      <c r="A3" s="14" t="s">
-        <v>175</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="s">
-        <v>184</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>218</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" s="14"/>
-      <c r="L3" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
-      <c r="A4" s="14" t="s">
-        <v>176</v>
-      </c>
-      <c r="B4" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" s="14"/>
-      <c r="E4" s="14"/>
-      <c r="F4" s="14"/>
-      <c r="G4" s="14"/>
-      <c r="H4" s="14"/>
-      <c r="I4" s="14"/>
-      <c r="J4" s="14"/>
-      <c r="K4" s="14"/>
-      <c r="L4" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
-      <c r="A5" s="14" t="s">
-        <v>177</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>207</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="F5" s="14" t="s">
-        <v>206</v>
-      </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="I5" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
-      <c r="A6" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>133</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>132</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>208</v>
-      </c>
-      <c r="E6" s="14" t="s">
-        <v>215</v>
-      </c>
-      <c r="F6" s="14" t="s">
-        <v>209</v>
-      </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="3" t="s">
-        <v>200</v>
-      </c>
-      <c r="I6" s="3" t="s">
-        <v>201</v>
-      </c>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
-      <c r="A7" s="14" t="s">
-        <v>179</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>169</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="D7" s="14" t="s">
-        <v>212</v>
-      </c>
-      <c r="E7" s="14" t="s">
-        <v>222</v>
-      </c>
-      <c r="F7" s="14" t="s">
-        <v>211</v>
-      </c>
-      <c r="G7" s="17">
-        <v>100</v>
-      </c>
-      <c r="H7" s="3" t="s">
-        <v>196</v>
-      </c>
-      <c r="I7" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" s="14"/>
-      <c r="L7" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
-      <c r="A8" s="14" t="s">
-        <v>232</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>112</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>111</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>233</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>231</v>
-      </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>234</v>
-      </c>
-      <c r="J8" s="14"/>
-      <c r="K8" s="14"/>
-      <c r="L8" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
-      <c r="A9" s="14" t="s">
-        <v>180</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="E9" s="14" t="s">
-        <v>197</v>
-      </c>
-      <c r="F9" s="14" t="s">
-        <v>210</v>
-      </c>
-      <c r="G9" s="14"/>
-      <c r="H9" s="14" t="s">
-        <v>198</v>
-      </c>
-      <c r="I9" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="J9" s="14"/>
-      <c r="K9" s="14"/>
-      <c r="L9" s="3" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
-      <c r="A10" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>84</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>214</v>
-      </c>
-      <c r="E10" s="14" t="s">
-        <v>223</v>
-      </c>
-      <c r="F10" s="14" t="s">
-        <v>213</v>
-      </c>
-      <c r="G10" s="14"/>
-      <c r="H10" s="3" t="s">
-        <v>227</v>
-      </c>
-      <c r="I10" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="J10" s="14"/>
-      <c r="K10" s="14"/>
-      <c r="L10" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
-      <c r="A11" s="14" t="s">
-        <v>182</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>74</v>
-      </c>
-      <c r="D11" s="14"/>
-      <c r="E11" s="14"/>
-      <c r="F11" s="14"/>
-      <c r="G11" s="14"/>
-      <c r="H11" s="14"/>
-      <c r="I11" s="14"/>
-      <c r="J11" s="14"/>
-      <c r="K11" s="14"/>
-      <c r="L11" s="3" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
-      <c r="A12" s="14" t="s">
-        <v>183</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="D12" s="14"/>
-      <c r="E12" s="14"/>
-      <c r="F12" s="14" t="s">
-        <v>199</v>
-      </c>
-      <c r="G12" s="14"/>
-      <c r="H12" s="14"/>
-      <c r="I12" s="14"/>
-      <c r="J12" s="14"/>
-      <c r="K12" s="14"/>
-      <c r="L12" s="3" t="s">
-        <v>171</v>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
+      <c r="K12" s="3" t="s">
+        <v>165</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB009834-6166-4820-A31D-8FA8521CE2FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834057DE-C9DE-4892-84E2-41B26A64BA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -2108,7 +2108,7 @@
     <col min="10" max="12" width="23.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" ht="33">
+    <row r="1" spans="1:14">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{834057DE-C9DE-4892-84E2-41B26A64BA64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439F1FA5-1B4E-4298-A5E6-27A996049399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="321" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="239">
   <si>
     <t>id</t>
   </si>
@@ -3191,7 +3191,7 @@
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
       <c r="K11" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="12" spans="1:12">
@@ -3215,6 +3215,9 @@
       <c r="J12" s="13"/>
       <c r="K12" s="3" t="s">
         <v>165</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>219</v>
       </c>
     </row>
   </sheetData>

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{439F1FA5-1B4E-4298-A5E6-27A996049399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A29D76-F407-4C88-8277-E8C9F891241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -3160,7 +3160,7 @@
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
       <c r="K10" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
     </row>
     <row r="11" spans="1:12">

--- a/assets/2026臺北數位藝術節_店家清冊.xlsx
+++ b/assets/2026臺北數位藝術節_店家清冊.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\user\Desktop\DAF2026\assets\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99A29D76-F407-4C88-8277-E8C9F891241F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5CF4204-731E-4E9F-9259-A1F0556E2597}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="2" xr2:uid="{6CF2F47F-369B-4526-8963-C11C1554301C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="316" uniqueCount="237">
   <si>
     <t>id</t>
   </si>
@@ -876,9 +876,6 @@
   </si>
   <si>
     <t>partnership-10</t>
-  </si>
-  <si>
-    <t>partnership-11</t>
   </si>
   <si>
     <t>Mirror of Erised
@@ -941,10 +938,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>響應優惠</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>CNSalon花草茶
 源起於火山口下的西恩花園新鮮採摘的一杯花草茶，如同「味蕾的花束」，將山裡日月積累的感受，透過一杯花草茶帶入每個人的生活，分享大自然的美好與能量。
 CNSalon花冰菓
@@ -1388,10 +1381,6 @@
   </si>
   <si>
     <t>CNSalon 火山口下的花茶店</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>拿掉</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
@@ -1599,6 +1588,10 @@
   </si>
   <si>
     <t>特製冰淇淋</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>隱藏</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2201,7 +2194,7 @@
         <v>130</v>
       </c>
       <c r="B3" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C3" s="5" t="s">
         <v>129</v>
@@ -2376,7 +2369,7 @@
         <v>91</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>90</v>
@@ -2663,10 +2656,10 @@
         <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>32</v>
@@ -2790,16 +2783,16 @@
         <v>22</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F5" s="3" t="s">
         <v>157</v>
@@ -2863,22 +2856,22 @@
         <v>164</v>
       </c>
       <c r="E1" s="15" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F1" s="15" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G1" s="15" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H1" s="15" t="s">
         <v>36</v>
       </c>
       <c r="I1" s="15" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J1" s="15" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="K1" s="15" t="s">
         <v>8</v>
@@ -2893,28 +2886,28 @@
         <v>151</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="K2" s="3" t="s">
         <v>167</v>
@@ -2931,19 +2924,19 @@
         <v>16</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I3" s="13"/>
       <c r="J3" s="13"/>
@@ -2953,7 +2946,7 @@
     </row>
     <row r="4" spans="1:12">
       <c r="A4" s="13" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>23</v>
@@ -2972,36 +2965,36 @@
         <v>165</v>
       </c>
       <c r="L4" s="3" t="s">
-        <v>219</v>
+        <v>236</v>
       </c>
     </row>
     <row r="5" spans="1:12">
       <c r="A5" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F5" s="13" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="J5" s="13"/>
       <c r="K5" s="3" t="s">
@@ -3013,25 +3006,25 @@
         <v>170</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="C6" s="5" t="s">
         <v>129</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="E6" s="13" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F6" s="13" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I6" s="13"/>
       <c r="J6" s="13"/>
@@ -3050,19 +3043,19 @@
         <v>119</v>
       </c>
       <c r="D7" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="I7" s="13"/>
       <c r="J7" s="13"/>
@@ -3072,7 +3065,7 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="13" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B8" s="5" t="s">
         <v>109</v>
@@ -3081,19 +3074,19 @@
         <v>108</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>209</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>213</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>211</v>
       </c>
-      <c r="E8" s="3" t="s">
-        <v>215</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>213</v>
-      </c>
       <c r="G8" s="3" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="I8" s="13"/>
       <c r="J8" s="13"/>
@@ -3112,19 +3105,19 @@
         <v>99</v>
       </c>
       <c r="D9" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="13" t="s">
+        <v>182</v>
+      </c>
+      <c r="F9" s="13" t="s">
+        <v>193</v>
+      </c>
+      <c r="G9" s="13" t="s">
         <v>183</v>
       </c>
-      <c r="E9" s="13" t="s">
-        <v>183</v>
-      </c>
-      <c r="F9" s="13" t="s">
-        <v>195</v>
-      </c>
-      <c r="G9" s="13" t="s">
-        <v>184</v>
-      </c>
       <c r="H9" s="13" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="I9" s="13"/>
       <c r="J9" s="13"/>
@@ -3143,19 +3136,19 @@
         <v>82</v>
       </c>
       <c r="D10" s="13" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="I10" s="13"/>
       <c r="J10" s="13"/>
@@ -3174,19 +3167,19 @@
         <v>72</v>
       </c>
       <c r="D11" s="13" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E11" s="17" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="F11" s="13" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="G11" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I11" s="13"/>
       <c r="J11" s="13"/>
@@ -3195,30 +3188,18 @@
       </c>
     </row>
     <row r="12" spans="1:12">
-      <c r="A12" s="13" t="s">
-        <v>175</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>50</v>
-      </c>
+      <c r="A12" s="13"/>
+      <c r="B12" s="5"/>
+      <c r="C12" s="5"/>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
-      <c r="F12" s="13" t="s">
-        <v>185</v>
-      </c>
+      <c r="F12" s="13"/>
       <c r="G12" s="13"/>
       <c r="H12" s="13"/>
       <c r="I12" s="13"/>
       <c r="J12" s="13"/>
-      <c r="K12" s="3" t="s">
-        <v>165</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>219</v>
-      </c>
+      <c r="K12" s="3"/>
+      <c r="L12" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
